--- a/excel/云下/云下物料.xlsx
+++ b/excel/云下/云下物料.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="722">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="738">
   <si>
     <t/>
   </si>
@@ -397,7 +397,7 @@
     <t>白参菌</t>
   </si>
   <si>
-    <t>北京旭日再升鸿经贸有限公司</t>
+    <t>北京旭日再升鸿经商贸有限公司</t>
   </si>
   <si>
     <t>白豆腐</t>
@@ -853,7 +853,7 @@
     <t>1006055</t>
   </si>
   <si>
-    <t>厨邦特级生抽</t>
+    <t>厨邦酱油</t>
   </si>
   <si>
     <t>820ml</t>
@@ -865,951 +865,954 @@
     <t>东古一品鲜酱油</t>
   </si>
   <si>
+    <t>500ml=500g</t>
+  </si>
+  <si>
+    <t>1006041</t>
+  </si>
+  <si>
+    <t>番茄沙司</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>1006006</t>
+  </si>
+  <si>
+    <t>海天老抽</t>
+  </si>
+  <si>
+    <t>4.82</t>
+  </si>
+  <si>
+    <t>海天生抽</t>
+  </si>
+  <si>
+    <t>1006050</t>
+  </si>
+  <si>
+    <t>蚝油</t>
+  </si>
+  <si>
+    <t>6000g</t>
+  </si>
+  <si>
+    <t>1006030</t>
+  </si>
+  <si>
+    <t>胡椒粉</t>
+  </si>
+  <si>
+    <t>510g</t>
+  </si>
+  <si>
+    <t>1006080</t>
+  </si>
+  <si>
+    <t>茴香籽粉</t>
+  </si>
+  <si>
+    <t>1006051</t>
+  </si>
+  <si>
+    <t>汇福大豆油</t>
+  </si>
+  <si>
+    <t>1桶=10kg 1kg=1000g</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>1005004</t>
+  </si>
+  <si>
+    <t>鸡汁</t>
+  </si>
+  <si>
+    <t>1006028</t>
+  </si>
+  <si>
+    <t>料酒</t>
+  </si>
+  <si>
+    <t>3.58</t>
+  </si>
+  <si>
+    <t>1006027</t>
+  </si>
+  <si>
+    <t>牛腩</t>
+  </si>
+  <si>
+    <t>1003004</t>
+  </si>
+  <si>
+    <t>去皮花生米</t>
+  </si>
+  <si>
+    <t>1001025</t>
+  </si>
+  <si>
+    <t>十三香</t>
+  </si>
+  <si>
+    <t>45g</t>
+  </si>
+  <si>
+    <t>3.2</t>
+  </si>
+  <si>
+    <t>1006075</t>
+  </si>
+  <si>
+    <t>水妈妈柠檬汁</t>
+  </si>
+  <si>
+    <t>1L</t>
+  </si>
+  <si>
+    <t>1006044</t>
+  </si>
+  <si>
+    <t>酸木瓜酸汤</t>
+  </si>
+  <si>
+    <t>500ml*20袋</t>
+  </si>
+  <si>
+    <t>390</t>
+  </si>
+  <si>
+    <t>1006069</t>
+  </si>
+  <si>
+    <t>泰式甜辣酱</t>
+  </si>
+  <si>
+    <t>835g</t>
+  </si>
+  <si>
+    <t>1006024</t>
+  </si>
+  <si>
+    <t>天立老醋</t>
+  </si>
+  <si>
+    <t>1006047</t>
+  </si>
+  <si>
+    <t>盐</t>
+  </si>
+  <si>
+    <t>400g</t>
+  </si>
+  <si>
+    <t>1006022</t>
+  </si>
+  <si>
+    <t>幺麻子木姜子油</t>
+  </si>
+  <si>
+    <t>250g</t>
+  </si>
+  <si>
+    <t>12.56</t>
+  </si>
+  <si>
+    <t>辣鲜露</t>
+  </si>
+  <si>
+    <t>1006016</t>
+  </si>
+  <si>
+    <t>鱼露</t>
+  </si>
+  <si>
+    <t>1006023</t>
+  </si>
+  <si>
+    <t>德式拉格</t>
+  </si>
+  <si>
+    <t>酒</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>大理市九寸奇妙发酵商贸有限责任公司</t>
+  </si>
+  <si>
+    <t>1008005</t>
+  </si>
+  <si>
+    <t>桂花小麦</t>
+  </si>
+  <si>
+    <t>128.04</t>
+  </si>
+  <si>
+    <t>1008004</t>
+  </si>
+  <si>
+    <t>椰乳</t>
+  </si>
+  <si>
+    <t>480</t>
+  </si>
+  <si>
+    <t>冠泉食品科技（北京）有限公司</t>
+  </si>
+  <si>
+    <t>1007009</t>
+  </si>
+  <si>
+    <t>冷冻菠萝</t>
+  </si>
+  <si>
+    <t>1箱=10袋 1袋=1000g</t>
+  </si>
+  <si>
+    <t>300</t>
+  </si>
+  <si>
+    <t>福运顺通(北京)贸易有公司</t>
+  </si>
+  <si>
+    <t>1002001</t>
+  </si>
+  <si>
+    <t>冷冻青豆</t>
+  </si>
+  <si>
+    <t>1Kg*10袋</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>十月稻田香米</t>
+  </si>
+  <si>
+    <t>1箱=8袋 1袋=3500g</t>
+  </si>
+  <si>
+    <t>276</t>
+  </si>
+  <si>
+    <t>1005012</t>
+  </si>
+  <si>
+    <t>油焖鸡醬</t>
+  </si>
+  <si>
+    <t>1kg*16袋</t>
+  </si>
+  <si>
+    <t>405</t>
+  </si>
+  <si>
+    <t>1009023</t>
+  </si>
+  <si>
+    <t>猪肉沫</t>
+  </si>
+  <si>
+    <t>640</t>
+  </si>
+  <si>
+    <t>1009026</t>
+  </si>
+  <si>
+    <t>罗非鱼</t>
+  </si>
+  <si>
+    <t>海鲜</t>
+  </si>
+  <si>
+    <t>5kg*2袋</t>
+  </si>
+  <si>
+    <t>350</t>
+  </si>
+  <si>
+    <t>聚百味国际贸易（北京）有限公司</t>
+  </si>
+  <si>
+    <t>1004001</t>
+  </si>
+  <si>
+    <t>青稞小米饼</t>
+  </si>
+  <si>
+    <t>400g*20包</t>
+  </si>
+  <si>
+    <t>1005010</t>
+  </si>
+  <si>
+    <t>无骨鸡爪</t>
+  </si>
+  <si>
+    <t>10000g</t>
+  </si>
+  <si>
+    <t>600</t>
+  </si>
+  <si>
+    <t>1009014</t>
+  </si>
+  <si>
+    <t>牛肝菌</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>上海鼎述贸易有限公司</t>
+  </si>
+  <si>
+    <t>350ml纸碗(云下)</t>
+  </si>
+  <si>
+    <t>易耗品</t>
+  </si>
+  <si>
+    <t>1000个</t>
+  </si>
+  <si>
+    <t>北京市博爱群技贸有限责任公司</t>
+  </si>
+  <si>
+    <t>2001001</t>
+  </si>
+  <si>
+    <t>360ml塑料杯</t>
+  </si>
+  <si>
+    <t>285</t>
+  </si>
+  <si>
+    <t>2001002</t>
+  </si>
+  <si>
+    <t>6寸汤勺</t>
+  </si>
+  <si>
+    <t>400</t>
+  </si>
+  <si>
+    <t>2001003</t>
+  </si>
+  <si>
+    <t>8寸本色椭圆盘(云下)</t>
+  </si>
+  <si>
+    <t>500个</t>
+  </si>
+  <si>
+    <t>2001004</t>
+  </si>
+  <si>
+    <t>L紫线手套</t>
+  </si>
+  <si>
+    <t>12双</t>
+  </si>
+  <si>
+    <t>2001005</t>
+  </si>
+  <si>
+    <t>N拉丝布（加粗）</t>
+  </si>
+  <si>
+    <t>卷</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>2001006</t>
+  </si>
+  <si>
+    <t>百洁布</t>
+  </si>
+  <si>
+    <t>2001008</t>
+  </si>
+  <si>
+    <t>玻璃刮</t>
+  </si>
+  <si>
+    <t>套</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>2001009</t>
+  </si>
+  <si>
+    <t>博爱硅油纸14*25cm</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>2001010</t>
+  </si>
+  <si>
+    <t>大收银纸(件)</t>
+  </si>
+  <si>
+    <t>228</t>
+  </si>
+  <si>
+    <t>2001011</t>
+  </si>
+  <si>
+    <t>得力0325订书器</t>
+  </si>
+  <si>
+    <t>个</t>
+  </si>
+  <si>
+    <t>2001012</t>
+  </si>
+  <si>
+    <t>地板清洁剂</t>
+  </si>
+  <si>
+    <t>2001013</t>
+  </si>
+  <si>
+    <t>订书订</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>2001014</t>
+  </si>
+  <si>
+    <t>防滑地垫（云下）</t>
+  </si>
+  <si>
+    <t>块</t>
+  </si>
+  <si>
+    <t>2001015</t>
+  </si>
+  <si>
+    <t>黑色垃圾袋(特级)</t>
+  </si>
+  <si>
+    <t>捆</t>
+  </si>
+  <si>
+    <t>2001016</t>
+  </si>
+  <si>
+    <t>黑色条帽（云下）</t>
+  </si>
+  <si>
+    <t>2001017</t>
+  </si>
+  <si>
+    <t>咖色方毛巾</t>
+  </si>
+  <si>
+    <t>2001019</t>
+  </si>
+  <si>
+    <t>蓝色擦杯布</t>
+  </si>
+  <si>
+    <t>2001021</t>
+  </si>
+  <si>
+    <t>冷饮杯盖</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>2001022</t>
+  </si>
+  <si>
+    <t>美泽保鲜袋（30*20）</t>
+  </si>
+  <si>
+    <t>200只</t>
+  </si>
+  <si>
+    <t>7.7</t>
+  </si>
+  <si>
+    <t>2001023</t>
+  </si>
+  <si>
+    <t>免洗洗手液（无酒精）</t>
+  </si>
+  <si>
+    <t>2001024</t>
+  </si>
+  <si>
+    <t>南孚电池5#</t>
+  </si>
+  <si>
+    <t>节</t>
+  </si>
+  <si>
+    <t>2.4</t>
+  </si>
+  <si>
+    <t>2001025</t>
+  </si>
+  <si>
+    <t>票叉</t>
+  </si>
+  <si>
+    <t>2001027</t>
+  </si>
+  <si>
+    <t>沙拉碗（云下1000ML)</t>
+  </si>
+  <si>
+    <t>600个</t>
+  </si>
+  <si>
+    <t>2001028</t>
+  </si>
+  <si>
+    <t>沙拉碗（云下500ml)</t>
+  </si>
+  <si>
+    <t>2001029</t>
+  </si>
+  <si>
+    <t>塑料盖（云下)</t>
+  </si>
+  <si>
+    <t>132</t>
+  </si>
+  <si>
+    <t>2001030</t>
+  </si>
+  <si>
+    <t>通版500ml玉米淀粉方盒</t>
+  </si>
+  <si>
+    <t>300个</t>
+  </si>
+  <si>
+    <t>216</t>
+  </si>
+  <si>
+    <t>2001031</t>
+  </si>
+  <si>
+    <t>无纺布袋（云下）</t>
+  </si>
+  <si>
+    <t>2001032</t>
+  </si>
+  <si>
+    <t>五月花厨房用纸</t>
+  </si>
+  <si>
+    <t>2001033</t>
+  </si>
+  <si>
+    <t>吸嘴袋（云下）</t>
+  </si>
+  <si>
+    <t>680</t>
+  </si>
+  <si>
+    <t>2001034</t>
+  </si>
+  <si>
+    <t>新越PVC保鲜膜</t>
+  </si>
+  <si>
+    <t>32.5</t>
+  </si>
+  <si>
+    <t>2001037</t>
+  </si>
+  <si>
+    <t>旋转墩布桶（k22)</t>
+  </si>
+  <si>
+    <t>1套</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>2001040</t>
+  </si>
+  <si>
+    <t>一次性纸杯（坐忘）</t>
+  </si>
+  <si>
+    <t>2001042</t>
+  </si>
+  <si>
+    <t>玉米淀粉酱料盒（云下）</t>
+  </si>
+  <si>
+    <t>1000套</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>2001043</t>
+  </si>
+  <si>
+    <t>云下保温袋</t>
+  </si>
+  <si>
+    <t>1.2</t>
+  </si>
+  <si>
+    <t>2001044</t>
+  </si>
+  <si>
+    <t>云下餐巾纸</t>
+  </si>
+  <si>
+    <t>2001045</t>
+  </si>
+  <si>
+    <t>云下餐具包</t>
+  </si>
+  <si>
+    <t>2001046</t>
+  </si>
+  <si>
+    <t>竹筷(云下）</t>
+  </si>
+  <si>
+    <t>100双</t>
+  </si>
+  <si>
+    <t>2001048</t>
+  </si>
+  <si>
+    <t>松毛尖</t>
+  </si>
+  <si>
+    <t>1kg</t>
+  </si>
+  <si>
+    <t>烧烤料</t>
+  </si>
+  <si>
+    <t>米布粉</t>
+  </si>
+  <si>
+    <t>云南白酒</t>
+  </si>
+  <si>
+    <t>10kg</t>
+  </si>
+  <si>
+    <t>巧家红糖</t>
+  </si>
+  <si>
+    <t>去骨鸡腿</t>
+  </si>
+  <si>
+    <t>奶白菜</t>
+  </si>
+  <si>
+    <t>杏鲍菇</t>
+  </si>
+  <si>
+    <t>香叶</t>
+  </si>
+  <si>
+    <t>去皮玉米</t>
+  </si>
+  <si>
+    <t>青彩椒</t>
+  </si>
+  <si>
+    <t>三黄鸡块</t>
+  </si>
+  <si>
+    <t>茴香</t>
+  </si>
+  <si>
+    <t>馒头</t>
+  </si>
+  <si>
+    <t>猪头肉</t>
+  </si>
+  <si>
+    <t>咸鸭蛋</t>
+  </si>
+  <si>
+    <t>秋葵</t>
+  </si>
+  <si>
+    <t>皱皮椒</t>
+  </si>
+  <si>
+    <t>木耳</t>
+  </si>
+  <si>
+    <t>娃娃菜</t>
+  </si>
+  <si>
+    <t>青豆</t>
+  </si>
+  <si>
+    <t>平菇</t>
+  </si>
+  <si>
+    <t>皮蛋</t>
+  </si>
+  <si>
+    <t>鲈鱼</t>
+  </si>
+  <si>
+    <t>咸蛋黄</t>
+  </si>
+  <si>
+    <t>芝麻酱</t>
+  </si>
+  <si>
+    <t>菠菜</t>
+  </si>
+  <si>
+    <t>圆白菜</t>
+  </si>
+  <si>
+    <t>翅中</t>
+  </si>
+  <si>
+    <t>面条</t>
+  </si>
+  <si>
+    <t>豇豆</t>
+  </si>
+  <si>
+    <t>绿豆芽</t>
+  </si>
+  <si>
+    <t>火腿肠</t>
+  </si>
+  <si>
+    <t>虾</t>
+  </si>
+  <si>
+    <t>大叶生菜</t>
+  </si>
+  <si>
+    <t>山药</t>
+  </si>
+  <si>
+    <t>玉米</t>
+  </si>
+  <si>
+    <t>红薯粉</t>
+  </si>
+  <si>
+    <t>味精</t>
+  </si>
+  <si>
+    <t>2000g</t>
+  </si>
+  <si>
+    <t>鱿鱼</t>
+  </si>
+  <si>
+    <t>饼丝</t>
+  </si>
+  <si>
+    <t>手剥笋</t>
+  </si>
+  <si>
+    <t>碎牛肉</t>
+  </si>
+  <si>
+    <t>长茄子</t>
+  </si>
+  <si>
+    <t>长方形薄饼</t>
+  </si>
+  <si>
+    <t>1箱=8包 1包=6片</t>
+  </si>
+  <si>
+    <t>烧椒酱</t>
+  </si>
+  <si>
+    <t>320g</t>
+  </si>
+  <si>
+    <t>淡奶油</t>
+  </si>
+  <si>
+    <t>1Kg</t>
+  </si>
+  <si>
+    <t>石屏豆腐豆丝</t>
+  </si>
+  <si>
+    <t>饮料打包袋</t>
+  </si>
+  <si>
+    <t>100个</t>
+  </si>
+  <si>
+    <t>前厅用纸</t>
+  </si>
+  <si>
+    <t>100抽</t>
+  </si>
+  <si>
+    <t>PLA吸管6mm*230mm</t>
+  </si>
+  <si>
+    <t>100根</t>
+  </si>
+  <si>
+    <t>南孚电池7#</t>
+  </si>
+  <si>
+    <t>板</t>
+  </si>
+  <si>
+    <t>4节</t>
+  </si>
+  <si>
+    <t>洗涤灵</t>
+  </si>
+  <si>
+    <t>丁晴手套</t>
+  </si>
+  <si>
+    <t>PLA吸管12mm*230mm</t>
+  </si>
+  <si>
+    <t>订书机</t>
+  </si>
+  <si>
+    <t>台</t>
+  </si>
+  <si>
+    <t>烤箱清洁片</t>
+  </si>
+  <si>
+    <t>100块</t>
+  </si>
+  <si>
+    <t>美式勺子</t>
+  </si>
+  <si>
+    <t>牙线（坐忘）</t>
+  </si>
+  <si>
+    <t>加长胶皮手套</t>
+  </si>
+  <si>
+    <t>双</t>
+  </si>
+  <si>
+    <t>1双</t>
+  </si>
+  <si>
+    <t>兰柏文80*30</t>
+  </si>
+  <si>
+    <t>200卷</t>
+  </si>
+  <si>
+    <t>580纸盒盖（300个）</t>
+  </si>
+  <si>
+    <t>580纸盒（300个）</t>
+  </si>
+  <si>
+    <t>洁地灵</t>
+  </si>
+  <si>
+    <t>10Kg</t>
+  </si>
+  <si>
+    <t>木筷(中华竹筷)</t>
+  </si>
+  <si>
+    <t>1000双</t>
+  </si>
+  <si>
+    <t>烧烤吸油纸</t>
+  </si>
+  <si>
+    <t>100张</t>
+  </si>
+  <si>
+    <t>西米罐头</t>
+  </si>
+  <si>
+    <t>900g</t>
+  </si>
+  <si>
+    <t>果糖糖浆</t>
+  </si>
+  <si>
+    <t>玉米淀粉</t>
+  </si>
+  <si>
+    <t>豆瓣酱</t>
+  </si>
+  <si>
+    <t>青花椒油</t>
+  </si>
+  <si>
+    <t>200ml</t>
+  </si>
+  <si>
+    <t>海天味极鲜</t>
+  </si>
+  <si>
+    <t>408ml</t>
+  </si>
+  <si>
+    <t>黑胡椒粉</t>
+  </si>
+  <si>
+    <t>425g</t>
+  </si>
+  <si>
+    <t>芫荽粉</t>
+  </si>
+  <si>
+    <t>海天海鲜酱油</t>
+  </si>
+  <si>
+    <t>鸡精</t>
+  </si>
+  <si>
+    <t>芒果酱</t>
+  </si>
+  <si>
+    <t>鲜萃茉莉茶饮</t>
+  </si>
+  <si>
+    <t>72度葡萄烈酒</t>
+  </si>
+  <si>
     <t>500ml</t>
   </si>
   <si>
-    <t>1006041</t>
-  </si>
-  <si>
-    <t>番茄沙司</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>1006006</t>
-  </si>
-  <si>
-    <t>海天老抽</t>
-  </si>
-  <si>
-    <t>4.82</t>
-  </si>
-  <si>
-    <t>海天生抽</t>
-  </si>
-  <si>
-    <t>1006050</t>
-  </si>
-  <si>
-    <t>蚝油</t>
-  </si>
-  <si>
-    <t>6000g</t>
-  </si>
-  <si>
-    <t>1006030</t>
-  </si>
-  <si>
-    <t>胡椒粉</t>
-  </si>
-  <si>
-    <t>510g</t>
-  </si>
-  <si>
-    <t>1006080</t>
-  </si>
-  <si>
-    <t>茴香籽粉</t>
-  </si>
-  <si>
-    <t>1006051</t>
-  </si>
-  <si>
-    <t>汇福大豆油</t>
-  </si>
-  <si>
-    <t>1桶=10kg 1kg=1000g</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>1005004</t>
-  </si>
-  <si>
-    <t>鸡汁</t>
-  </si>
-  <si>
-    <t>1006028</t>
-  </si>
-  <si>
-    <t>料酒</t>
-  </si>
-  <si>
-    <t>3.58</t>
-  </si>
-  <si>
-    <t>1006027</t>
-  </si>
-  <si>
-    <t>牛腩</t>
-  </si>
-  <si>
-    <t>1003004</t>
-  </si>
-  <si>
-    <t>去皮花生米</t>
-  </si>
-  <si>
-    <t>1001025</t>
-  </si>
-  <si>
-    <t>十三香</t>
-  </si>
-  <si>
-    <t>45g</t>
-  </si>
-  <si>
-    <t>3.2</t>
-  </si>
-  <si>
-    <t>1006075</t>
-  </si>
-  <si>
-    <t>水妈妈柠檬汁</t>
-  </si>
-  <si>
-    <t>1L</t>
-  </si>
-  <si>
-    <t>1006044</t>
-  </si>
-  <si>
-    <t>酸木瓜酸汤</t>
-  </si>
-  <si>
-    <t>500ml*20袋</t>
-  </si>
-  <si>
-    <t>390</t>
-  </si>
-  <si>
-    <t>1006069</t>
-  </si>
-  <si>
-    <t>泰式甜辣酱</t>
-  </si>
-  <si>
-    <t>835g</t>
-  </si>
-  <si>
-    <t>1006024</t>
-  </si>
-  <si>
-    <t>天立老醋</t>
-  </si>
-  <si>
-    <t>1006047</t>
-  </si>
-  <si>
-    <t>盐</t>
-  </si>
-  <si>
-    <t>400g</t>
-  </si>
-  <si>
-    <t>1006022</t>
-  </si>
-  <si>
-    <t>幺麻子木姜子油</t>
-  </si>
-  <si>
-    <t>250g</t>
-  </si>
-  <si>
-    <t>12.56</t>
-  </si>
-  <si>
-    <t>辣鲜露</t>
-  </si>
-  <si>
-    <t>1006016</t>
-  </si>
-  <si>
-    <t>鱼露</t>
-  </si>
-  <si>
-    <t>1006023</t>
-  </si>
-  <si>
-    <t>德式拉格</t>
-  </si>
-  <si>
-    <t>酒</t>
-  </si>
-  <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>大理市九寸奇妙发酵商贸有限责任公司</t>
-  </si>
-  <si>
-    <t>1008005</t>
-  </si>
-  <si>
-    <t>桂花小麦</t>
-  </si>
-  <si>
-    <t>128.04</t>
-  </si>
-  <si>
-    <t>1008004</t>
-  </si>
-  <si>
-    <t>椰乳</t>
-  </si>
-  <si>
-    <t>480</t>
-  </si>
-  <si>
-    <t>冠泉食品科技（北京）有限公司</t>
-  </si>
-  <si>
-    <t>1007009</t>
-  </si>
-  <si>
-    <t>冷冻菠萝</t>
-  </si>
-  <si>
-    <t>1箱=10kg 1kg=1000g</t>
-  </si>
-  <si>
-    <t>300</t>
-  </si>
-  <si>
-    <t>福运顺通(北京)贸易有公司</t>
-  </si>
-  <si>
-    <t>1002001</t>
-  </si>
-  <si>
-    <t>冷冻青豆</t>
-  </si>
-  <si>
-    <t>1Kg*10袋</t>
-  </si>
-  <si>
-    <t>95</t>
-  </si>
-  <si>
-    <t>十月稻田香米</t>
-  </si>
-  <si>
-    <t>1箱=8袋 1袋=3500g</t>
-  </si>
-  <si>
-    <t>276</t>
-  </si>
-  <si>
-    <t>1005012</t>
-  </si>
-  <si>
-    <t>油焖鸡醬</t>
-  </si>
-  <si>
-    <t>1kg*16袋</t>
-  </si>
-  <si>
-    <t>405</t>
-  </si>
-  <si>
-    <t>1009023</t>
-  </si>
-  <si>
-    <t>猪肉沫</t>
-  </si>
-  <si>
-    <t>640</t>
-  </si>
-  <si>
-    <t>1009026</t>
-  </si>
-  <si>
-    <t>罗非鱼块</t>
-  </si>
-  <si>
-    <t>海鲜</t>
-  </si>
-  <si>
-    <t>5kg*2袋</t>
-  </si>
-  <si>
-    <t>350</t>
-  </si>
-  <si>
-    <t>聚百味国际贸易（北京）有限公司</t>
-  </si>
-  <si>
-    <t>1004001</t>
-  </si>
-  <si>
-    <t>青稞小米饼</t>
-  </si>
-  <si>
-    <t>400g*20包</t>
-  </si>
-  <si>
-    <t>1005010</t>
-  </si>
-  <si>
-    <t>无骨鸡爪</t>
-  </si>
-  <si>
-    <t>10000g</t>
-  </si>
-  <si>
-    <t>600</t>
-  </si>
-  <si>
-    <t>1009014</t>
-  </si>
-  <si>
-    <t>牛肝菌</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>上海鼎述贸易有限公司</t>
-  </si>
-  <si>
-    <t>350ml纸碗(云下)</t>
-  </si>
-  <si>
-    <t>易耗品</t>
-  </si>
-  <si>
-    <t>1000个</t>
-  </si>
-  <si>
-    <t>北京市博爱群技贸有限责任公司</t>
-  </si>
-  <si>
-    <t>2001001</t>
-  </si>
-  <si>
-    <t>360ml塑料杯</t>
-  </si>
-  <si>
-    <t>285</t>
-  </si>
-  <si>
-    <t>2001002</t>
-  </si>
-  <si>
-    <t>6寸汤勺</t>
-  </si>
-  <si>
-    <t>400</t>
-  </si>
-  <si>
-    <t>2001003</t>
-  </si>
-  <si>
-    <t>8寸本色椭圆盘(云下)</t>
-  </si>
-  <si>
-    <t>500个</t>
-  </si>
-  <si>
-    <t>2001004</t>
-  </si>
-  <si>
-    <t>L紫线手套</t>
-  </si>
-  <si>
-    <t>12双</t>
-  </si>
-  <si>
-    <t>2001005</t>
-  </si>
-  <si>
-    <t>N拉丝布（加粗）</t>
-  </si>
-  <si>
-    <t>卷</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>2001006</t>
-  </si>
-  <si>
-    <t>百洁布</t>
-  </si>
-  <si>
-    <t>2001008</t>
-  </si>
-  <si>
-    <t>玻璃刮</t>
-  </si>
-  <si>
-    <t>套</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>2001009</t>
-  </si>
-  <si>
-    <t>博爱硅油纸14*25cm</t>
-  </si>
-  <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>2001010</t>
-  </si>
-  <si>
-    <t>大收银纸(件)</t>
-  </si>
-  <si>
-    <t>228</t>
-  </si>
-  <si>
-    <t>2001011</t>
-  </si>
-  <si>
-    <t>得力0325订书器</t>
-  </si>
-  <si>
-    <t>个</t>
-  </si>
-  <si>
-    <t>2001012</t>
-  </si>
-  <si>
-    <t>地板清洁剂</t>
-  </si>
-  <si>
-    <t>2001013</t>
-  </si>
-  <si>
-    <t>订书订</t>
-  </si>
-  <si>
-    <t>1.5</t>
-  </si>
-  <si>
-    <t>2001014</t>
-  </si>
-  <si>
-    <t>防滑地垫（云下）</t>
-  </si>
-  <si>
-    <t>块</t>
-  </si>
-  <si>
-    <t>2001015</t>
-  </si>
-  <si>
-    <t>黑色垃圾袋(特级)</t>
-  </si>
-  <si>
-    <t>捆</t>
-  </si>
-  <si>
-    <t>2001016</t>
-  </si>
-  <si>
-    <t>黑色条帽（云下）</t>
-  </si>
-  <si>
-    <t>2001017</t>
-  </si>
-  <si>
-    <t>咖色方毛巾</t>
-  </si>
-  <si>
-    <t>2001019</t>
-  </si>
-  <si>
-    <t>蓝色擦杯布</t>
-  </si>
-  <si>
-    <t>2001021</t>
-  </si>
-  <si>
-    <t>冷饮杯盖</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>2001022</t>
-  </si>
-  <si>
-    <t>美泽保鲜袋（30*20）</t>
-  </si>
-  <si>
-    <t>200只</t>
-  </si>
-  <si>
-    <t>7.7</t>
-  </si>
-  <si>
-    <t>2001023</t>
-  </si>
-  <si>
-    <t>免洗洗手液（无酒精）</t>
-  </si>
-  <si>
-    <t>2001024</t>
-  </si>
-  <si>
-    <t>南孚电池5#</t>
-  </si>
-  <si>
-    <t>节</t>
-  </si>
-  <si>
-    <t>2.4</t>
-  </si>
-  <si>
-    <t>2001025</t>
-  </si>
-  <si>
-    <t>票叉</t>
-  </si>
-  <si>
-    <t>2001027</t>
-  </si>
-  <si>
-    <t>沙拉碗（云下1000ML)</t>
-  </si>
-  <si>
-    <t>600个</t>
-  </si>
-  <si>
-    <t>2001028</t>
-  </si>
-  <si>
-    <t>沙拉碗（云下500ml)</t>
-  </si>
-  <si>
-    <t>2001029</t>
-  </si>
-  <si>
-    <t>塑料盖（云下)</t>
-  </si>
-  <si>
-    <t>132</t>
-  </si>
-  <si>
-    <t>2001030</t>
-  </si>
-  <si>
-    <t>通版500ml玉米淀粉方盒</t>
-  </si>
-  <si>
-    <t>300个</t>
-  </si>
-  <si>
-    <t>216</t>
-  </si>
-  <si>
-    <t>2001031</t>
-  </si>
-  <si>
-    <t>无纺布袋（云下）</t>
-  </si>
-  <si>
-    <t>2001032</t>
-  </si>
-  <si>
-    <t>五月花厨房用纸</t>
-  </si>
-  <si>
-    <t>2001033</t>
-  </si>
-  <si>
-    <t>吸嘴袋（云下）</t>
-  </si>
-  <si>
-    <t>680</t>
-  </si>
-  <si>
-    <t>2001034</t>
-  </si>
-  <si>
-    <t>新越PVC保鲜膜</t>
-  </si>
-  <si>
-    <t>32.5</t>
-  </si>
-  <si>
-    <t>2001037</t>
-  </si>
-  <si>
-    <t>旋转墩布桶（k22)</t>
-  </si>
-  <si>
-    <t>1套</t>
-  </si>
-  <si>
-    <t>85</t>
-  </si>
-  <si>
-    <t>2001040</t>
-  </si>
-  <si>
-    <t>一次性纸杯（坐忘）</t>
-  </si>
-  <si>
-    <t>2001042</t>
-  </si>
-  <si>
-    <t>玉米淀粉酱料盒（云下）</t>
-  </si>
-  <si>
-    <t>1000套</t>
-  </si>
-  <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>2001043</t>
-  </si>
-  <si>
-    <t>云下保温袋</t>
-  </si>
-  <si>
-    <t>1.2</t>
-  </si>
-  <si>
-    <t>2001044</t>
-  </si>
-  <si>
-    <t>云下餐巾纸</t>
-  </si>
-  <si>
-    <t>2001045</t>
-  </si>
-  <si>
-    <t>云下餐具包</t>
-  </si>
-  <si>
-    <t>2001046</t>
-  </si>
-  <si>
-    <t>竹筷(云下）</t>
-  </si>
-  <si>
-    <t>100双</t>
-  </si>
-  <si>
-    <t>2001048</t>
-  </si>
-  <si>
-    <t>松毛尖</t>
-  </si>
-  <si>
-    <t>1kg</t>
-  </si>
-  <si>
-    <t>烧烤料</t>
-  </si>
-  <si>
-    <t>米布粉</t>
-  </si>
-  <si>
-    <t>云南白酒</t>
-  </si>
-  <si>
-    <t>10kg</t>
-  </si>
-  <si>
-    <t>巧家红糖</t>
-  </si>
-  <si>
-    <t>去骨鸡腿</t>
-  </si>
-  <si>
-    <t>奶白菜</t>
-  </si>
-  <si>
-    <t>杏鲍菇</t>
-  </si>
-  <si>
-    <t>香叶</t>
-  </si>
-  <si>
-    <t>去皮玉米</t>
-  </si>
-  <si>
-    <t>青彩椒</t>
-  </si>
-  <si>
-    <t>三黄鸡块</t>
-  </si>
-  <si>
-    <t>茴香</t>
-  </si>
-  <si>
-    <t>馒头</t>
-  </si>
-  <si>
-    <t>猪头肉</t>
-  </si>
-  <si>
-    <t>咸鸭蛋</t>
-  </si>
-  <si>
-    <t>秋葵</t>
-  </si>
-  <si>
-    <t>皱皮椒</t>
-  </si>
-  <si>
-    <t>木耳</t>
-  </si>
-  <si>
-    <t>娃娃菜</t>
-  </si>
-  <si>
-    <t>青豆</t>
-  </si>
-  <si>
-    <t>平菇</t>
-  </si>
-  <si>
-    <t>皮蛋</t>
-  </si>
-  <si>
-    <t>鲈鱼</t>
-  </si>
-  <si>
-    <t>咸蛋黄</t>
-  </si>
-  <si>
-    <t>芝麻酱</t>
-  </si>
-  <si>
-    <t>菠菜</t>
-  </si>
-  <si>
-    <t>圆白菜</t>
-  </si>
-  <si>
-    <t>翅中</t>
-  </si>
-  <si>
-    <t>面条</t>
-  </si>
-  <si>
-    <t>豇豆</t>
-  </si>
-  <si>
-    <t>绿豆芽</t>
-  </si>
-  <si>
-    <t>火腿肠</t>
-  </si>
-  <si>
-    <t>虾</t>
-  </si>
-  <si>
-    <t>大叶生菜</t>
-  </si>
-  <si>
-    <t>山药</t>
-  </si>
-  <si>
-    <t>玉米</t>
-  </si>
-  <si>
-    <t>红薯粉</t>
-  </si>
-  <si>
-    <t>味精</t>
-  </si>
-  <si>
-    <t>2000g</t>
-  </si>
-  <si>
-    <t>鱿鱼</t>
-  </si>
-  <si>
-    <t>饼丝</t>
-  </si>
-  <si>
-    <t>手剥笋</t>
-  </si>
-  <si>
-    <t>碎牛肉</t>
-  </si>
-  <si>
-    <t>长茄子</t>
-  </si>
-  <si>
-    <t>长方形薄饼</t>
-  </si>
-  <si>
-    <t>1箱=8包 1包=6片</t>
-  </si>
-  <si>
-    <t>烧椒酱</t>
-  </si>
-  <si>
-    <t>320g</t>
-  </si>
-  <si>
-    <t>淡奶油</t>
-  </si>
-  <si>
-    <t>1Kg</t>
-  </si>
-  <si>
-    <t>石屏豆腐豆丝</t>
-  </si>
-  <si>
-    <t>饮料打包袋</t>
-  </si>
-  <si>
-    <t>100个</t>
-  </si>
-  <si>
-    <t>前厅用纸</t>
-  </si>
-  <si>
-    <t>100抽</t>
-  </si>
-  <si>
-    <t>PLA吸管6mm*230mm</t>
-  </si>
-  <si>
-    <t>100根</t>
-  </si>
-  <si>
-    <t>南孚电池7#</t>
-  </si>
-  <si>
-    <t>板</t>
-  </si>
-  <si>
-    <t>4节</t>
-  </si>
-  <si>
-    <t>洗涤灵</t>
-  </si>
-  <si>
-    <t>丁晴手套</t>
-  </si>
-  <si>
-    <t>PLA吸管12mm*230mm</t>
-  </si>
-  <si>
-    <t>订书机</t>
-  </si>
-  <si>
-    <t>台</t>
-  </si>
-  <si>
-    <t>烤箱清洁片</t>
-  </si>
-  <si>
-    <t>100块</t>
-  </si>
-  <si>
-    <t>美式勺子</t>
-  </si>
-  <si>
-    <t>牙线（坐忘）</t>
-  </si>
-  <si>
-    <t>加长胶皮手套</t>
-  </si>
-  <si>
-    <t>双</t>
-  </si>
-  <si>
-    <t>1双</t>
-  </si>
-  <si>
-    <t>兰柏文80*30</t>
-  </si>
-  <si>
-    <t>200卷</t>
-  </si>
-  <si>
-    <t>580纸盒盖（300个）</t>
-  </si>
-  <si>
-    <t>580纸盒（300个）</t>
-  </si>
-  <si>
-    <t>洁地灵</t>
-  </si>
-  <si>
-    <t>10Kg</t>
-  </si>
-  <si>
-    <t>木筷(中华竹筷)</t>
-  </si>
-  <si>
-    <t>1000双</t>
-  </si>
-  <si>
-    <t>烧烤吸油纸</t>
-  </si>
-  <si>
-    <t>100张</t>
-  </si>
-  <si>
-    <t>西米罐头</t>
-  </si>
-  <si>
-    <t>900g</t>
-  </si>
-  <si>
-    <t>果糖糖浆</t>
-  </si>
-  <si>
-    <t>玉米淀粉</t>
-  </si>
-  <si>
-    <t>豆瓣酱</t>
-  </si>
-  <si>
-    <t>青花椒油</t>
-  </si>
-  <si>
-    <t>200ml</t>
-  </si>
-  <si>
-    <t>海天味极鲜</t>
-  </si>
-  <si>
-    <t>408ml</t>
-  </si>
-  <si>
-    <t>黑胡椒粉</t>
-  </si>
-  <si>
-    <t>425g</t>
-  </si>
-  <si>
-    <t>芫荽粉</t>
-  </si>
-  <si>
-    <t>海天海鲜酱油</t>
-  </si>
-  <si>
-    <t>鸡精</t>
-  </si>
-  <si>
-    <t>芒果酱</t>
-  </si>
-  <si>
-    <t>鲜萃茉莉茶饮</t>
-  </si>
-  <si>
-    <t>72度葡萄烈酒</t>
-  </si>
-  <si>
     <t>自采</t>
   </si>
   <si>
@@ -1855,18 +1858,12 @@
     <t>鸡肉</t>
   </si>
   <si>
-    <t>北京旭日再升鸿经商贸有限公司</t>
-  </si>
-  <si>
     <t>马苏碎</t>
   </si>
   <si>
     <t>3500g</t>
   </si>
   <si>
-    <t>福运顺通（北京）贸易有限公司</t>
-  </si>
-  <si>
     <t>猪油</t>
   </si>
   <si>
@@ -1910,9 +1907,6 @@
   </si>
   <si>
     <t>青稞粑粑</t>
-  </si>
-  <si>
-    <t>聚百味国际贸易（北京)有限公司</t>
   </si>
   <si>
     <t xml:space="preserve">煮炖
@@ -2187,7 +2181,61 @@
     <t>牛肉</t>
   </si>
   <si>
+    <t>鲤鱼</t>
+  </si>
+  <si>
+    <t>心里美萝卜</t>
+  </si>
+  <si>
+    <t>蒿子秆</t>
+  </si>
+  <si>
+    <t>油麦菜</t>
+  </si>
+  <si>
+    <t>梅花肉</t>
+  </si>
+  <si>
+    <t>青笋</t>
+  </si>
+  <si>
+    <t>虾籽粉</t>
+  </si>
+  <si>
+    <t>榨菜</t>
+  </si>
+  <si>
+    <t>熟白芝麻</t>
+  </si>
+  <si>
+    <t>柠檬酸汤</t>
+  </si>
+  <si>
+    <t>1箱=20包 1包=500g</t>
+  </si>
+  <si>
+    <t>冷冻猪蹄</t>
+  </si>
+  <si>
+    <t>1箱=10公斤</t>
+  </si>
+  <si>
     <t>包浆豆腐1</t>
+  </si>
+  <si>
+    <t>1箱=22条</t>
+  </si>
+  <si>
+    <t>订书针</t>
+  </si>
+  <si>
+    <t>美泽保鲜袋</t>
+  </si>
+  <si>
+    <t>烤箱药片</t>
+  </si>
+  <si>
+    <t>820g</t>
   </si>
 </sst>
 </file>
@@ -2314,6 +2362,9 @@
     <xf fontId="8" fillId="0" borderId="0" xfId="0">
       <alignment vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
     </xf>
+    <xf fontId="3" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf fontId="9" fillId="0" borderId="0" xfId="0">
@@ -2334,9 +2385,6 @@
     <xf numFmtId="300" fontId="11" fillId="3" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf fontId="3" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-    </xf>
     <xf fontId="10" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles>
@@ -2668,7 +2716,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
-  <dimension ref="H359"/>
+  <dimension ref="H368"/>
   <cols>
     <col min="1" max="1" width="28.2109" customWidth="1"/>
     <col min="4" max="4" width="29.3125" customWidth="1"/>
@@ -3473,7 +3521,7 @@
         <v>27</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G31" s="4" t="s">
         <v>32</v>
@@ -3499,7 +3547,7 @@
         <v>130</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G32" s="4" t="s">
         <v>32</v>
@@ -3525,7 +3573,7 @@
         <v>132</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G33" s="4" t="s">
         <v>32</v>
@@ -3551,7 +3599,7 @@
         <v>58</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G34" s="4" t="s">
         <v>32</v>
@@ -3577,7 +3625,7 @@
         <v>136</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G35" s="4" t="s">
         <v>32</v>
@@ -3603,7 +3651,7 @@
         <v>139</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G36" s="4" t="s">
         <v>32</v>
@@ -3629,7 +3677,7 @@
         <v>27</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G37" s="4" t="s">
         <v>32</v>
@@ -3655,7 +3703,7 @@
         <v>92</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G38" s="4" t="s">
         <v>28</v>
@@ -3681,7 +3729,7 @@
         <v>145</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G39" s="4" t="s">
         <v>32</v>
@@ -3707,7 +3755,7 @@
         <v>147</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G40" s="4" t="s">
         <v>32</v>
@@ -3733,7 +3781,7 @@
         <v>150</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G41" s="4" t="s">
         <v>32</v>
@@ -3759,7 +3807,7 @@
         <v>153</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G42" s="4" t="s">
         <v>28</v>
@@ -3785,7 +3833,7 @@
         <v>156</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G43" s="4" t="s">
         <v>32</v>
@@ -3811,7 +3859,7 @@
         <v>159</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G44" s="4" t="s">
         <v>32</v>
@@ -3837,7 +3885,7 @@
         <v>132</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G45" s="4" t="s">
         <v>32</v>
@@ -3866,7 +3914,7 @@
         <v>163</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G46" s="4" t="s">
         <v>32</v>
@@ -3892,7 +3940,7 @@
         <v>166</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G47" s="4" t="s">
         <v>32</v>
@@ -3918,7 +3966,7 @@
         <v>169</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G48" s="4" t="s">
         <v>32</v>
@@ -3944,7 +3992,7 @@
         <v>171</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G49" s="4" t="s">
         <v>55</v>
@@ -3970,7 +4018,7 @@
         <v>174</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G50" s="4" t="s">
         <v>59</v>
@@ -3996,7 +4044,7 @@
         <v>177</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G51" s="4" t="s">
         <v>59</v>
@@ -4022,7 +4070,7 @@
         <v>179</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G52" s="4" t="s">
         <v>32</v>
@@ -4048,7 +4096,7 @@
         <v>130</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G53" s="4" t="s">
         <v>32</v>
@@ -4074,7 +4122,7 @@
         <v>27</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G54" s="4" t="s">
         <v>32</v>
@@ -4100,7 +4148,7 @@
         <v>185</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G55" s="4" t="s">
         <v>32</v>
@@ -4126,7 +4174,7 @@
         <v>132</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G56" s="4" t="s">
         <v>32</v>
@@ -4152,7 +4200,7 @@
         <v>27</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G57" s="4" t="s">
         <v>32</v>
@@ -4178,7 +4226,7 @@
         <v>171</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G58" s="4" t="s">
         <v>32</v>
@@ -4204,7 +4252,7 @@
         <v>194</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G59" s="4" t="s">
         <v>32</v>
@@ -4230,7 +4278,7 @@
         <v>103</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G60" s="4" t="s">
         <v>32</v>
@@ -4256,7 +4304,7 @@
         <v>65</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G61" s="4" t="s">
         <v>59</v>
@@ -4282,7 +4330,7 @@
         <v>136</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G62" s="4" t="s">
         <v>32</v>
@@ -4308,7 +4356,7 @@
         <v>27</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G63" s="4" t="s">
         <v>32</v>
@@ -4334,7 +4382,7 @@
         <v>206</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G64" s="4" t="s">
         <v>32</v>
@@ -4360,7 +4408,7 @@
         <v>174</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G65" s="4" t="s">
         <v>32</v>
@@ -4386,7 +4434,7 @@
         <v>210</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G66" s="4" t="s">
         <v>32</v>
@@ -4412,7 +4460,7 @@
         <v>147</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G67" s="4" t="s">
         <v>32</v>
@@ -4438,7 +4486,7 @@
         <v>171</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G68" s="4" t="s">
         <v>32</v>
@@ -4464,7 +4512,7 @@
         <v>132</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G69" s="4" t="s">
         <v>32</v>
@@ -4490,7 +4538,7 @@
         <v>218</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G70" s="4" t="s">
         <v>32</v>
@@ -4516,7 +4564,7 @@
         <v>156</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G71" s="4" t="s">
         <v>32</v>
@@ -4542,7 +4590,7 @@
         <v>50</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G72" s="4" t="s">
         <v>32</v>
@@ -4568,7 +4616,7 @@
         <v>136</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G73" s="4" t="s">
         <v>32</v>
@@ -4594,7 +4642,7 @@
         <v>226</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G74" s="4" t="s">
         <v>32</v>
@@ -4620,7 +4668,7 @@
         <v>156</v>
       </c>
       <c r="F75" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G75" s="4" t="s">
         <v>32</v>
@@ -4646,7 +4694,7 @@
         <v>185</v>
       </c>
       <c r="F76" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G76" s="4" t="s">
         <v>32</v>
@@ -4672,7 +4720,7 @@
         <v>179</v>
       </c>
       <c r="F77" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G77" s="4" t="s">
         <v>32</v>
@@ -4698,7 +4746,7 @@
         <v>136</v>
       </c>
       <c r="F78" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G78" s="4" t="s">
         <v>32</v>
@@ -4724,7 +4772,7 @@
         <v>236</v>
       </c>
       <c r="F79" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G79" s="4" t="s">
         <v>32</v>
@@ -4750,7 +4798,7 @@
         <v>50</v>
       </c>
       <c r="F80" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G80" s="4" t="s">
         <v>32</v>
@@ -4776,7 +4824,7 @@
         <v>241</v>
       </c>
       <c r="F81" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G81" s="4" t="s">
         <v>32</v>
@@ -4802,7 +4850,7 @@
         <v>103</v>
       </c>
       <c r="F82" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G82" s="4" t="s">
         <v>32</v>
@@ -4828,7 +4876,7 @@
         <v>177</v>
       </c>
       <c r="F83" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G83" s="4" t="s">
         <v>32</v>
@@ -4854,7 +4902,7 @@
         <v>156</v>
       </c>
       <c r="F84" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G84" s="4" t="s">
         <v>32</v>
@@ -4880,7 +4928,7 @@
         <v>27</v>
       </c>
       <c r="F85" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G85" s="4" t="s">
         <v>32</v>
@@ -4906,7 +4954,7 @@
         <v>132</v>
       </c>
       <c r="F86" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G86" s="4" t="s">
         <v>32</v>
@@ -4932,7 +4980,7 @@
         <v>27</v>
       </c>
       <c r="F87" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G87" s="4" t="s">
         <v>32</v>
@@ -4958,7 +5006,7 @@
         <v>62</v>
       </c>
       <c r="F88" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G88" s="4" t="s">
         <v>32</v>
@@ -4984,7 +5032,7 @@
         <v>241</v>
       </c>
       <c r="F89" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G89" s="4" t="s">
         <v>32</v>
@@ -5010,7 +5058,7 @@
         <v>259</v>
       </c>
       <c r="F90" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G90" s="4" t="s">
         <v>32</v>
@@ -5036,7 +5084,7 @@
         <v>27</v>
       </c>
       <c r="F91" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G91" s="4" t="s">
         <v>32</v>
@@ -5062,7 +5110,7 @@
         <v>92</v>
       </c>
       <c r="F92" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G92" s="4" t="s">
         <v>32</v>
@@ -5088,7 +5136,7 @@
         <v>103</v>
       </c>
       <c r="F93" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G93" s="4" t="s">
         <v>32</v>
@@ -5114,7 +5162,7 @@
         <v>267</v>
       </c>
       <c r="F94" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G94" s="4" t="s">
         <v>32</v>
@@ -5140,7 +5188,7 @@
         <v>130</v>
       </c>
       <c r="F95" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G95" s="4" t="s">
         <v>32</v>
@@ -5238,7 +5286,7 @@
         <v>25</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>280</v>
+        <v>737</v>
       </c>
       <c r="E99" s="7">
         <v>17</v>
@@ -5264,7 +5312,7 @@
         <v>25</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>283</v>
+        <v>46</v>
       </c>
       <c r="E100" s="7">
         <v>8</v>
@@ -5679,8 +5727,8 @@
       <c r="C116" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D116" s="4" t="s">
-        <v>46</v>
+      <c r="D116" s="5" t="s">
+        <v>199</v>
       </c>
       <c r="E116" s="4" t="s">
         <v>307</v>
@@ -5861,7 +5909,7 @@
       <c r="C123" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="D123" s="4" t="s">
+      <c r="D123" s="5" t="s">
         <v>122</v>
       </c>
       <c r="E123" s="4" t="s">
@@ -6008,7 +6056,7 @@
       </c>
     </row>
     <row r="129" spans="1:8">
-      <c r="A129" s="4" t="s">
+      <c r="A129" s="5" t="s">
         <v>370</v>
       </c>
       <c r="B129" s="4" t="s">
@@ -6017,8 +6065,8 @@
       <c r="C129" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="D129" s="4" t="s">
-        <v>372</v>
+      <c r="D129" s="5" t="s">
+        <v>733</v>
       </c>
       <c r="E129" s="4" t="s">
         <v>373</v>
@@ -6425,7 +6473,7 @@
     </row>
     <row r="145" spans="1:8">
       <c r="A145" s="5" t="s">
-        <v>424</v>
+        <v>734</v>
       </c>
       <c r="B145" s="4" t="s">
         <v>18</v>
@@ -6607,7 +6655,7 @@
     </row>
     <row r="152" spans="1:8">
       <c r="A152" s="5" t="s">
-        <v>442</v>
+        <v>735</v>
       </c>
       <c r="B152" s="4" t="s">
         <v>404</v>
@@ -7116,7 +7164,7 @@
         <v>4</v>
       </c>
       <c r="F171" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G171" s="4" t="s">
         <v>32</v>
@@ -7142,7 +7190,7 @@
         <v>28</v>
       </c>
       <c r="F172" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G172" s="4" t="s">
         <v>32</v>
@@ -7168,7 +7216,7 @@
         <v>29</v>
       </c>
       <c r="F173" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G173" s="4" t="s">
         <v>32</v>
@@ -7246,7 +7294,7 @@
         <v>13.8</v>
       </c>
       <c r="F176" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G176" s="4" t="s">
         <v>32</v>
@@ -7272,7 +7320,7 @@
         <v>6.5</v>
       </c>
       <c r="F177" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G177" s="4" t="s">
         <v>32</v>
@@ -7298,7 +7346,7 @@
         <v>7.63</v>
       </c>
       <c r="F178" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G178" s="4" t="s">
         <v>32</v>
@@ -7324,7 +7372,7 @@
         <v>21</v>
       </c>
       <c r="F179" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G179" s="4" t="s">
         <v>32</v>
@@ -7350,7 +7398,7 @@
         <v>7.5</v>
       </c>
       <c r="F180" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G180" s="4" t="s">
         <v>32</v>
@@ -7376,7 +7424,7 @@
         <v>4.5</v>
       </c>
       <c r="F181" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G181" s="4" t="s">
         <v>32</v>
@@ -7402,7 +7450,7 @@
         <v>12.5</v>
       </c>
       <c r="F182" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G182" s="4" t="s">
         <v>32</v>
@@ -7428,7 +7476,7 @@
         <v>5</v>
       </c>
       <c r="F183" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G183" s="4" t="s">
         <v>32</v>
@@ -7454,7 +7502,7 @@
         <v>0.7</v>
       </c>
       <c r="F184" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G184" s="4" t="s">
         <v>32</v>
@@ -7480,7 +7528,7 @@
         <v>30.52</v>
       </c>
       <c r="F185" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G185" s="4" t="s">
         <v>32</v>
@@ -7506,7 +7554,7 @@
         <v>10</v>
       </c>
       <c r="F186" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G186" s="4" t="s">
         <v>32</v>
@@ -7532,7 +7580,7 @@
         <v>20</v>
       </c>
       <c r="F187" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G187" s="4" t="s">
         <v>32</v>
@@ -7558,7 +7606,7 @@
         <v>8.5</v>
       </c>
       <c r="F188" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G188" s="4" t="s">
         <v>32</v>
@@ -7584,7 +7632,7 @@
         <v>8.5</v>
       </c>
       <c r="F189" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G189" s="4" t="s">
         <v>32</v>
@@ -7610,7 +7658,7 @@
         <v>5.5</v>
       </c>
       <c r="F190" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G190" s="4" t="s">
         <v>32</v>
@@ -7636,7 +7684,7 @@
         <v>20</v>
       </c>
       <c r="F191" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G191" s="4" t="s">
         <v>32</v>
@@ -7662,7 +7710,7 @@
         <v>5</v>
       </c>
       <c r="F192" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G192" s="4" t="s">
         <v>32</v>
@@ -7688,7 +7736,7 @@
         <v>10</v>
       </c>
       <c r="F193" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G193" s="4" t="s">
         <v>32</v>
@@ -7714,7 +7762,7 @@
         <v>28</v>
       </c>
       <c r="F194" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G194" s="4" t="s">
         <v>32</v>
@@ -7740,7 +7788,7 @@
         <v>18</v>
       </c>
       <c r="F195" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G195" s="4" t="s">
         <v>32</v>
@@ -7766,7 +7814,7 @@
         <v>18</v>
       </c>
       <c r="F196" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G196" s="4" t="s">
         <v>32</v>
@@ -7792,7 +7840,7 @@
         <v>4</v>
       </c>
       <c r="F197" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G197" s="4" t="s">
         <v>32</v>
@@ -7818,7 +7866,7 @@
         <v>2.6</v>
       </c>
       <c r="F198" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G198" s="4" t="s">
         <v>32</v>
@@ -7844,7 +7892,7 @@
         <v>26.5</v>
       </c>
       <c r="F199" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G199" s="4" t="s">
         <v>32</v>
@@ -7870,7 +7918,7 @@
         <v>3</v>
       </c>
       <c r="F200" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G200" s="4" t="s">
         <v>32</v>
@@ -7896,7 +7944,7 @@
         <v>6</v>
       </c>
       <c r="F201" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G201" s="4" t="s">
         <v>32</v>
@@ -7922,7 +7970,7 @@
         <v>1.5</v>
       </c>
       <c r="F202" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G202" s="4" t="s">
         <v>32</v>
@@ -7948,7 +7996,7 @@
         <v>17</v>
       </c>
       <c r="F203" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G203" s="4" t="s">
         <v>32</v>
@@ -7974,7 +8022,7 @@
         <v>38</v>
       </c>
       <c r="F204" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G204" s="4" t="s">
         <v>32</v>
@@ -8000,7 +8048,7 @@
         <v>5.5</v>
       </c>
       <c r="F205" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G205" s="4" t="s">
         <v>32</v>
@@ -8026,7 +8074,7 @@
         <v>7.8</v>
       </c>
       <c r="F206" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G206" s="4" t="s">
         <v>32</v>
@@ -8052,7 +8100,7 @@
         <v>6.5</v>
       </c>
       <c r="F207" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G207" s="4" t="s">
         <v>32</v>
@@ -8078,7 +8126,7 @@
         <v>6.5</v>
       </c>
       <c r="F208" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G208" s="4" t="s">
         <v>32</v>
@@ -8130,7 +8178,7 @@
         <v>30</v>
       </c>
       <c r="F210" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G210" s="4" t="s">
         <v>32</v>
@@ -8156,7 +8204,7 @@
         <v>3</v>
       </c>
       <c r="F211" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G211" s="4" t="s">
         <v>32</v>
@@ -8182,7 +8230,7 @@
         <v>7</v>
       </c>
       <c r="F212" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G212" s="4" t="s">
         <v>32</v>
@@ -8234,7 +8282,7 @@
         <v>5</v>
       </c>
       <c r="F214" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G214" s="4" t="s">
         <v>32</v>
@@ -8286,7 +8334,7 @@
         <v>23</v>
       </c>
       <c r="F216" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G216" s="4" t="s">
         <v>32</v>
@@ -8312,7 +8360,7 @@
         <v>47.5</v>
       </c>
       <c r="F217" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G217" s="4" t="s">
         <v>32</v>
@@ -8557,7 +8605,7 @@
     </row>
     <row r="227" spans="1:8">
       <c r="A227" s="5" t="s">
-        <v>564</v>
+        <v>736</v>
       </c>
       <c r="B227" s="4" t="s">
         <v>18</v>
@@ -9164,13 +9212,13 @@
         <v>340</v>
       </c>
       <c r="D250" s="4" t="s">
-        <v>283</v>
+        <v>598</v>
       </c>
       <c r="E250" s="4">
         <v>180</v>
       </c>
       <c r="F250" s="4" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="G250" s="4" t="s">
         <v>109</v>
@@ -9181,7 +9229,7 @@
     </row>
     <row r="251" spans="1:8">
       <c r="A251" s="4" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B251" s="4" t="s">
         <v>24</v>
@@ -9190,13 +9238,13 @@
         <v>340</v>
       </c>
       <c r="D251" s="4" t="s">
-        <v>600</v>
-      </c>
-      <c r="E251" s="4">
-        <v>68</v>
+        <v>601</v>
+      </c>
+      <c r="E251" s="7">
+        <v>38</v>
       </c>
       <c r="F251" s="4" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="G251" s="4" t="s">
         <v>109</v>
@@ -9207,7 +9255,7 @@
     </row>
     <row r="252" spans="1:8">
       <c r="A252" s="4" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B252" s="4" t="s">
         <v>24</v>
@@ -9216,13 +9264,13 @@
         <v>340</v>
       </c>
       <c r="D252" s="4" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="E252" s="4">
         <v>80</v>
       </c>
       <c r="F252" s="4" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="G252" s="4" t="s">
         <v>109</v>
@@ -9233,7 +9281,7 @@
     </row>
     <row r="253" spans="1:8">
       <c r="A253" s="4" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B253" s="4" t="s">
         <v>35</v>
@@ -9242,7 +9290,7 @@
         <v>106</v>
       </c>
       <c r="D253" s="4" t="s">
-        <v>283</v>
+        <v>598</v>
       </c>
       <c r="E253" s="4">
         <v>3.5</v>
@@ -9259,7 +9307,7 @@
     </row>
     <row r="254" spans="1:8">
       <c r="A254" s="4" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B254" s="4" t="s">
         <v>45</v>
@@ -9268,7 +9316,7 @@
         <v>106</v>
       </c>
       <c r="D254" s="4" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="E254" s="4">
         <v>12</v>
@@ -9285,7 +9333,7 @@
     </row>
     <row r="255" spans="1:8">
       <c r="A255" s="4" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B255" s="4" t="s">
         <v>112</v>
@@ -9294,7 +9342,7 @@
         <v>106</v>
       </c>
       <c r="D255" s="4" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="E255" s="4">
         <v>297.5</v>
@@ -9311,7 +9359,7 @@
     </row>
     <row r="256" spans="1:8">
       <c r="A256" s="4" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B256" s="4" t="s">
         <v>35</v>
@@ -9320,13 +9368,13 @@
         <v>19</v>
       </c>
       <c r="D256" s="4" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="E256" s="4">
         <v>4.5</v>
       </c>
       <c r="F256" s="4" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="G256" s="4" t="s">
         <v>109</v>
@@ -9337,7 +9385,7 @@
     </row>
     <row r="257" spans="1:8">
       <c r="A257" s="4" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B257" s="4" t="s">
         <v>24</v>
@@ -9346,7 +9394,7 @@
         <v>25</v>
       </c>
       <c r="D257" s="4" t="s">
-        <v>283</v>
+        <v>598</v>
       </c>
       <c r="E257" s="4">
         <v>8</v>
@@ -9355,7 +9403,7 @@
         <v>271</v>
       </c>
       <c r="G257" s="4" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H257" s="4">
         <v>1006062</v>
@@ -9363,7 +9411,7 @@
     </row>
     <row r="258" spans="1:8">
       <c r="A258" s="4" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B258" s="4" t="s">
         <v>10</v>
@@ -9378,10 +9426,10 @@
         <v>14.5</v>
       </c>
       <c r="F258" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G258" s="4" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H258" s="4">
         <v>1006067</v>
@@ -9407,7 +9455,7 @@
         <v>354</v>
       </c>
       <c r="G259" s="4" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H259" s="4">
         <v>1009027</v>
@@ -9415,7 +9463,7 @@
     </row>
     <row r="260" spans="1:8">
       <c r="A260" s="4" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B260" s="4" t="s">
         <v>276</v>
@@ -9424,7 +9472,7 @@
         <v>25</v>
       </c>
       <c r="D260" s="4" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="E260" s="4">
         <v>226</v>
@@ -9433,7 +9481,7 @@
         <v>271</v>
       </c>
       <c r="G260" s="4" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H260" s="4">
         <v>1005009</v>
@@ -9441,7 +9489,7 @@
     </row>
     <row r="261" spans="1:8">
       <c r="A261" s="11" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B261" s="11" t="s">
         <v>10</v>
@@ -9456,7 +9504,7 @@
         <v>48.5</v>
       </c>
       <c r="F261" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G261" s="12" t="s">
         <v>32</v>
@@ -9467,7 +9515,7 @@
     </row>
     <row r="262" spans="1:8">
       <c r="A262" s="11" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B262" s="11" t="s">
         <v>10</v>
@@ -9493,7 +9541,7 @@
     </row>
     <row r="263" spans="1:8">
       <c r="A263" s="11" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B263" s="11" t="s">
         <v>24</v>
@@ -9519,7 +9567,7 @@
     </row>
     <row r="264" spans="1:8">
       <c r="A264" s="11" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B264" s="11" t="s">
         <v>24</v>
@@ -9528,13 +9576,13 @@
         <v>106</v>
       </c>
       <c r="D264" s="11" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="E264" s="6">
         <v>30</v>
       </c>
       <c r="F264" s="6" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="G264" s="13" t="s">
         <v>109</v>
@@ -9545,7 +9593,7 @@
     </row>
     <row r="265" spans="1:8">
       <c r="A265" s="11" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B265" s="11" t="s">
         <v>24</v>
@@ -9571,7 +9619,7 @@
     </row>
     <row r="266" spans="1:8">
       <c r="A266" s="11" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B266" s="11" t="s">
         <v>10</v>
@@ -9597,7 +9645,7 @@
     </row>
     <row r="267" spans="1:8">
       <c r="A267" s="11" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B267" s="11" t="s">
         <v>24</v>
@@ -9606,13 +9654,13 @@
         <v>25</v>
       </c>
       <c r="D267" s="11" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E267" s="6">
         <v>117.6</v>
       </c>
       <c r="F267" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G267" s="12" t="s">
         <v>32</v>
@@ -9623,7 +9671,7 @@
     </row>
     <row r="268" spans="1:8">
       <c r="A268" s="11" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B268" s="11" t="s">
         <v>24</v>
@@ -9632,13 +9680,13 @@
         <v>106</v>
       </c>
       <c r="D268" s="11" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="E268" s="6">
         <v>38</v>
       </c>
       <c r="F268" s="6" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="G268" s="13" t="s">
         <v>109</v>
@@ -9649,7 +9697,7 @@
     </row>
     <row r="269" spans="1:8">
       <c r="A269" s="11" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B269" s="11" t="s">
         <v>35</v>
@@ -9667,7 +9715,7 @@
         <v>374</v>
       </c>
       <c r="G269" s="12" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="H269" s="11">
         <v>1006064</v>
@@ -9675,7 +9723,7 @@
     </row>
     <row r="270" spans="1:8">
       <c r="A270" s="5" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B270" s="5" t="s">
         <v>10</v>
@@ -9689,8 +9737,8 @@
       <c r="E270" s="7">
         <v>26</v>
       </c>
-      <c r="F270" s="25" t="s">
-        <v>613</v>
+      <c r="F270" s="15" t="s">
+        <v>127</v>
       </c>
       <c r="G270" s="5" t="s">
         <v>32</v>
@@ -9700,34 +9748,34 @@
       </c>
     </row>
     <row r="271" spans="1:8">
-      <c r="A271" s="15" t="s">
-        <v>635</v>
-      </c>
-      <c r="B271" s="15" t="s">
+      <c r="A271" s="16" t="s">
+        <v>633</v>
+      </c>
+      <c r="B271" s="16" t="s">
         <v>10</v>
       </c>
       <c r="C271" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D271" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="E271" s="16">
+      <c r="D271" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E271" s="17">
         <v>18</v>
       </c>
       <c r="F271" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="G271" s="15" t="s">
-        <v>611</v>
-      </c>
-      <c r="H271" s="16">
+        <v>127</v>
+      </c>
+      <c r="G271" s="16" t="s">
+        <v>612</v>
+      </c>
+      <c r="H271" s="17">
         <v>1006070</v>
       </c>
     </row>
     <row r="272" spans="1:8">
       <c r="A272" s="11" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B272" s="11" t="s">
         <v>10</v>
@@ -9742,18 +9790,18 @@
         <v>20</v>
       </c>
       <c r="F272" s="11" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="G272" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="H272" s="17">
+      <c r="H272" s="18">
         <v>1001107</v>
       </c>
     </row>
     <row r="273" spans="1:8">
       <c r="A273" s="11" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B273" s="11" t="s">
         <v>10</v>
@@ -9768,18 +9816,18 @@
         <v>20</v>
       </c>
       <c r="F273" s="11" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="G273" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="H273" s="17">
+      <c r="H273" s="18">
         <v>1001108</v>
       </c>
     </row>
     <row r="274" spans="1:8">
       <c r="A274" s="11" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B274" s="11" t="s">
         <v>24</v>
@@ -9788,7 +9836,7 @@
         <v>25</v>
       </c>
       <c r="D274" s="11" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="E274" s="11">
         <v>50</v>
@@ -9799,16 +9847,16 @@
       <c r="G274" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="H274" s="17">
+      <c r="H274" s="18">
         <v>1006086</v>
       </c>
     </row>
     <row r="275" spans="1:8">
       <c r="A275" s="11" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B275" s="11" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C275" s="4" t="s">
         <v>11</v>
@@ -9820,10 +9868,10 @@
         <v>90</v>
       </c>
       <c r="F275" s="11" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="G275" s="9" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="H275" s="6">
         <v>1001109</v>
@@ -9831,7 +9879,7 @@
     </row>
     <row r="276" spans="1:8">
       <c r="A276" s="11" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B276" s="11" t="s">
         <v>10</v>
@@ -9846,18 +9894,18 @@
         <v>50</v>
       </c>
       <c r="F276" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G276" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="H276" s="17">
+      <c r="H276" s="18">
         <v>1006001</v>
       </c>
     </row>
     <row r="277" spans="1:8">
-      <c r="A277" s="18" t="s">
-        <v>644</v>
+      <c r="A277" s="19" t="s">
+        <v>642</v>
       </c>
       <c r="B277" s="11" t="s">
         <v>428</v>
@@ -9877,13 +9925,13 @@
       <c r="G277" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="H277" s="17">
+      <c r="H277" s="18">
         <v>1009016</v>
       </c>
     </row>
     <row r="278" spans="1:8">
       <c r="A278" s="11" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="B278" s="11" t="s">
         <v>35</v>
@@ -9903,13 +9951,13 @@
       <c r="G278" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="H278" s="17">
+      <c r="H278" s="18">
         <v>1005015</v>
       </c>
     </row>
     <row r="279" spans="1:8">
       <c r="A279" s="11" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B279" s="11" t="s">
         <v>10</v>
@@ -9924,18 +9972,18 @@
         <v>62</v>
       </c>
       <c r="F279" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="G279" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="H279" s="20" t="s">
-        <v>647</v>
+        <v>127</v>
+      </c>
+      <c r="G279" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="H279" s="21" t="s">
+        <v>645</v>
       </c>
     </row>
     <row r="280" spans="1:8">
       <c r="A280" s="11" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B280" s="11" t="s">
         <v>35</v>
@@ -9952,16 +10000,16 @@
       <c r="F280" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G280" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="H280" s="17">
+      <c r="G280" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="H280" s="18">
         <v>1009036</v>
       </c>
     </row>
     <row r="281" spans="1:8">
-      <c r="A281" s="21" t="s">
-        <v>649</v>
+      <c r="A281" s="22" t="s">
+        <v>647</v>
       </c>
       <c r="B281" s="11" t="s">
         <v>35</v>
@@ -9978,16 +10026,16 @@
       <c r="F281" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G281" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="H281" s="17">
+      <c r="G281" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="H281" s="18">
         <v>1009035</v>
       </c>
     </row>
     <row r="282" spans="1:8">
       <c r="A282" s="11" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B282" s="11" t="s">
         <v>10</v>
@@ -10002,18 +10050,18 @@
         <v>5</v>
       </c>
       <c r="F282" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="G282" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="H282" s="17">
+        <v>127</v>
+      </c>
+      <c r="G282" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="H282" s="18">
         <v>1001038</v>
       </c>
     </row>
     <row r="283" spans="1:8">
       <c r="A283" s="11" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B283" s="11" t="s">
         <v>10</v>
@@ -10028,18 +10076,18 @@
         <v>3.5</v>
       </c>
       <c r="F283" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="G283" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="H283" s="17">
+        <v>127</v>
+      </c>
+      <c r="G283" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="H283" s="18">
         <v>1001110</v>
       </c>
     </row>
     <row r="284" spans="1:8">
       <c r="A284" s="11" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B284" s="11" t="s">
         <v>10</v>
@@ -10054,18 +10102,18 @@
         <v>3.5</v>
       </c>
       <c r="F284" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="G284" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="H284" s="17">
+        <v>127</v>
+      </c>
+      <c r="G284" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="H284" s="18">
         <v>1001111</v>
       </c>
     </row>
     <row r="285" spans="1:8">
       <c r="A285" s="11" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B285" s="11" t="s">
         <v>10</v>
@@ -10080,18 +10128,18 @@
         <v>180</v>
       </c>
       <c r="F285" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="G285" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="H285" s="17">
+        <v>127</v>
+      </c>
+      <c r="G285" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="H285" s="18">
         <v>1007014</v>
       </c>
     </row>
     <row r="286" spans="1:8">
       <c r="A286" s="11" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B286" s="11" t="s">
         <v>10</v>
@@ -10106,18 +10154,18 @@
         <v>150</v>
       </c>
       <c r="F286" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="G286" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="H286" s="20" t="s">
-        <v>655</v>
+        <v>127</v>
+      </c>
+      <c r="G286" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="H286" s="21" t="s">
+        <v>653</v>
       </c>
     </row>
     <row r="287" spans="1:8">
       <c r="A287" s="11" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B287" s="11" t="s">
         <v>10</v>
@@ -10132,18 +10180,18 @@
         <v>6.5</v>
       </c>
       <c r="F287" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="G287" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="H287" s="20" t="s">
-        <v>657</v>
+        <v>127</v>
+      </c>
+      <c r="G287" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="H287" s="21" t="s">
+        <v>655</v>
       </c>
     </row>
     <row r="288" spans="1:8">
       <c r="A288" s="11" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B288" s="11" t="s">
         <v>10</v>
@@ -10158,18 +10206,18 @@
         <v>11.5</v>
       </c>
       <c r="F288" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="G288" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="H288" s="17">
+        <v>127</v>
+      </c>
+      <c r="G288" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="H288" s="18">
         <v>1003027</v>
       </c>
     </row>
     <row r="289" spans="1:9">
       <c r="A289" s="11" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B289" s="11" t="s">
         <v>10</v>
@@ -10184,19 +10232,19 @@
         <v>8</v>
       </c>
       <c r="F289" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="G289" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="H289" s="17">
+        <v>127</v>
+      </c>
+      <c r="G289" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="H289" s="18">
         <v>1001113</v>
       </c>
-      <c r="I289" s="17" t="s"/>
+      <c r="I289" s="18" t="s"/>
     </row>
     <row r="290" spans="1:8">
       <c r="A290" s="11" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B290" s="11" t="s">
         <v>10</v>
@@ -10211,18 +10259,18 @@
         <v>6.5</v>
       </c>
       <c r="F290" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="G290" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="H290" s="17">
+        <v>127</v>
+      </c>
+      <c r="G290" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="H290" s="18">
         <v>1001050</v>
       </c>
     </row>
     <row r="291" spans="1:8">
       <c r="A291" s="11" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B291" s="11" t="s">
         <v>35</v>
@@ -10237,18 +10285,18 @@
         <v>6.5</v>
       </c>
       <c r="F291" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="G291" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="H291" s="17">
+        <v>127</v>
+      </c>
+      <c r="G291" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="H291" s="18">
         <v>1001114</v>
       </c>
     </row>
     <row r="292" spans="1:8">
       <c r="A292" s="11" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B292" s="11" t="s">
         <v>10</v>
@@ -10263,18 +10311,18 @@
         <v>5</v>
       </c>
       <c r="F292" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="G292" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="H292" s="17">
+        <v>127</v>
+      </c>
+      <c r="G292" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="H292" s="18">
         <v>1001115</v>
       </c>
     </row>
     <row r="293" spans="1:8">
       <c r="A293" s="11" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B293" s="11" t="s">
         <v>10</v>
@@ -10289,18 +10337,18 @@
         <v>18.5</v>
       </c>
       <c r="F293" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="G293" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="H293" s="17">
+        <v>127</v>
+      </c>
+      <c r="G293" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="H293" s="18">
         <v>1003012</v>
       </c>
     </row>
     <row r="294" spans="1:8">
       <c r="A294" s="11" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B294" s="11" t="s">
         <v>10</v>
@@ -10315,18 +10363,18 @@
         <v>7.5</v>
       </c>
       <c r="F294" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="G294" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="H294" s="17">
+        <v>127</v>
+      </c>
+      <c r="G294" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="H294" s="18">
         <v>1002005</v>
       </c>
     </row>
     <row r="295" spans="1:8">
       <c r="A295" s="11" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="B295" s="11" t="s">
         <v>10</v>
@@ -10341,18 +10389,18 @@
         <v>16</v>
       </c>
       <c r="F295" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="G295" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="H295" s="17">
+        <v>127</v>
+      </c>
+      <c r="G295" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="H295" s="18">
         <v>1001116</v>
       </c>
     </row>
     <row r="296" spans="1:8">
       <c r="A296" s="11" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B296" s="11" t="s">
         <v>10</v>
@@ -10367,18 +10415,18 @@
         <v>8.6</v>
       </c>
       <c r="F296" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="G296" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="H296" s="20" t="s">
-        <v>667</v>
+        <v>127</v>
+      </c>
+      <c r="G296" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="H296" s="21" t="s">
+        <v>665</v>
       </c>
     </row>
     <row r="297" spans="1:8">
       <c r="A297" s="11" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="B297" s="11" t="s">
         <v>10</v>
@@ -10393,18 +10441,18 @@
         <v>20</v>
       </c>
       <c r="F297" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="G297" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="H297" s="17">
+        <v>127</v>
+      </c>
+      <c r="G297" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="H297" s="18">
         <v>1001117</v>
       </c>
     </row>
     <row r="298" spans="1:8">
       <c r="A298" s="11" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B298" s="11" t="s">
         <v>10</v>
@@ -10419,18 +10467,18 @@
         <v>7.5</v>
       </c>
       <c r="F298" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="G298" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="H298" s="17">
+        <v>127</v>
+      </c>
+      <c r="G298" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="H298" s="18">
         <v>1001118</v>
       </c>
     </row>
     <row r="299" spans="1:8">
       <c r="A299" s="11" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B299" s="11" t="s">
         <v>35</v>
@@ -10445,18 +10493,18 @@
         <v>32.8</v>
       </c>
       <c r="F299" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="G299" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="H299" s="17">
+        <v>127</v>
+      </c>
+      <c r="G299" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="H299" s="18">
         <v>1001119</v>
       </c>
     </row>
     <row r="300" spans="1:8">
       <c r="A300" s="11" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="B300" s="11" t="s">
         <v>10</v>
@@ -10471,18 +10519,18 @@
         <v>4</v>
       </c>
       <c r="F300" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="G300" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="H300" s="17">
+        <v>127</v>
+      </c>
+      <c r="G300" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="H300" s="18">
         <v>1001120</v>
       </c>
     </row>
     <row r="301" spans="1:8">
       <c r="A301" s="11" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="B301" s="11" t="s">
         <v>24</v>
@@ -10497,18 +10545,18 @@
         <v>5</v>
       </c>
       <c r="F301" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="G301" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="H301" s="17">
+        <v>127</v>
+      </c>
+      <c r="G301" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="H301" s="18">
         <v>1005005</v>
       </c>
     </row>
     <row r="302" spans="1:8">
       <c r="A302" s="11" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="B302" s="11" t="s">
         <v>10</v>
@@ -10523,18 +10571,18 @@
         <v>48</v>
       </c>
       <c r="F302" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="G302" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="H302" s="20" t="s">
-        <v>674</v>
+        <v>127</v>
+      </c>
+      <c r="G302" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="H302" s="21" t="s">
+        <v>672</v>
       </c>
     </row>
     <row r="303" spans="1:8">
       <c r="A303" s="11" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="B303" s="11" t="s">
         <v>276</v>
@@ -10549,18 +10597,18 @@
         <v>27.1</v>
       </c>
       <c r="F303" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="G303" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="H303" s="17">
+        <v>127</v>
+      </c>
+      <c r="G303" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="H303" s="18">
         <v>1006087</v>
       </c>
     </row>
     <row r="304" spans="1:8">
       <c r="A304" s="11" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="B304" s="11" t="s">
         <v>112</v>
@@ -10577,16 +10625,16 @@
       <c r="F304" s="11" t="s">
         <v>389</v>
       </c>
-      <c r="G304" s="19" t="s">
-        <v>677</v>
-      </c>
-      <c r="H304" s="17">
+      <c r="G304" s="20" t="s">
+        <v>675</v>
+      </c>
+      <c r="H304" s="18">
         <v>2001060</v>
       </c>
     </row>
     <row r="305" spans="1:8">
       <c r="A305" s="11" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="B305" s="11" t="s">
         <v>112</v>
@@ -10603,16 +10651,16 @@
       <c r="F305" s="11" t="s">
         <v>389</v>
       </c>
-      <c r="G305" s="19" t="s">
-        <v>677</v>
-      </c>
-      <c r="H305" s="17">
+      <c r="G305" s="20" t="s">
+        <v>675</v>
+      </c>
+      <c r="H305" s="18">
         <v>2001061</v>
       </c>
     </row>
     <row r="306" spans="1:8">
       <c r="A306" s="11" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="B306" s="11" t="s">
         <v>24</v>
@@ -10629,16 +10677,16 @@
       <c r="F306" s="11" t="s">
         <v>271</v>
       </c>
-      <c r="G306" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="H306" s="17">
+      <c r="G306" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="H306" s="18">
         <v>1006088</v>
       </c>
     </row>
     <row r="307" spans="1:8">
       <c r="A307" s="11" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B307" s="11" t="s">
         <v>35</v>
@@ -10654,15 +10702,15 @@
         <v>271</v>
       </c>
       <c r="G307" s="9" t="s">
-        <v>611</v>
-      </c>
-      <c r="H307" s="17">
+        <v>612</v>
+      </c>
+      <c r="H307" s="18">
         <v>1006089</v>
       </c>
     </row>
     <row r="308" spans="1:8">
       <c r="A308" s="11" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B308" s="11" t="s">
         <v>10</v>
@@ -10677,18 +10725,18 @@
         <v>22</v>
       </c>
       <c r="F308" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G308" s="9" t="s">
-        <v>611</v>
-      </c>
-      <c r="H308" s="17">
+        <v>612</v>
+      </c>
+      <c r="H308" s="18">
         <v>1006090</v>
       </c>
     </row>
     <row r="309" spans="1:8">
       <c r="A309" s="11" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B309" s="11" t="s">
         <v>35</v>
@@ -10706,15 +10754,15 @@
         <v>354</v>
       </c>
       <c r="G309" s="9" t="s">
-        <v>611</v>
-      </c>
-      <c r="H309" s="17">
+        <v>612</v>
+      </c>
+      <c r="H309" s="18">
         <v>1006091</v>
       </c>
     </row>
     <row r="310" spans="1:8">
       <c r="A310" s="11" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B310" s="11" t="s">
         <v>35</v>
@@ -10729,18 +10777,18 @@
         <v>110</v>
       </c>
       <c r="F310" s="11" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="G310" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="H310" s="17">
+      <c r="H310" s="18">
         <v>1007022</v>
       </c>
     </row>
     <row r="311" spans="1:8">
       <c r="A311" s="11" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B311" s="11" t="s">
         <v>10</v>
@@ -10755,18 +10803,18 @@
         <v>68</v>
       </c>
       <c r="F311" s="11" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="G311" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="H311" s="17">
+      <c r="H311" s="18">
         <v>1007023</v>
       </c>
     </row>
     <row r="312" spans="1:8">
       <c r="A312" s="11" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B312" s="11" t="s">
         <v>10</v>
@@ -10781,18 +10829,18 @@
         <v>32</v>
       </c>
       <c r="F312" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G312" s="9" t="s">
-        <v>611</v>
-      </c>
-      <c r="H312" s="17">
+        <v>612</v>
+      </c>
+      <c r="H312" s="18">
         <v>1006063</v>
       </c>
     </row>
     <row r="313" spans="1:8">
       <c r="A313" s="11" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B313" s="11" t="s">
         <v>112</v>
@@ -10801,24 +10849,24 @@
         <v>25</v>
       </c>
       <c r="D313" s="11" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="E313" s="11">
         <v>450</v>
       </c>
       <c r="F313" s="11" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="G313" s="9" t="s">
-        <v>611</v>
-      </c>
-      <c r="H313" s="17">
+        <v>612</v>
+      </c>
+      <c r="H313" s="18">
         <v>1006092</v>
       </c>
     </row>
     <row r="314" spans="1:8">
       <c r="A314" s="11" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="B314" s="11" t="s">
         <v>428</v>
@@ -10833,18 +10881,18 @@
         <v>7.8</v>
       </c>
       <c r="F314" s="11" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="G314" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="H314" s="17">
+      <c r="H314" s="18">
         <v>1009031</v>
       </c>
     </row>
     <row r="315" spans="1:8">
       <c r="A315" s="11" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="B315" s="11" t="s">
         <v>10</v>
@@ -10859,18 +10907,18 @@
         <v>14.5</v>
       </c>
       <c r="F315" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G315" s="9" t="s">
-        <v>611</v>
-      </c>
-      <c r="H315" s="17">
+        <v>612</v>
+      </c>
+      <c r="H315" s="18">
         <v>1003005</v>
       </c>
     </row>
     <row r="316" spans="1:8">
       <c r="A316" s="11" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="B316" s="11" t="s">
         <v>404</v>
@@ -10879,7 +10927,7 @@
         <v>387</v>
       </c>
       <c r="D316" s="11" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="E316" s="11">
         <v>32.5</v>
@@ -10887,16 +10935,16 @@
       <c r="F316" s="11" t="s">
         <v>389</v>
       </c>
-      <c r="G316" s="19" t="s">
-        <v>677</v>
-      </c>
-      <c r="H316" s="17">
+      <c r="G316" s="20" t="s">
+        <v>675</v>
+      </c>
+      <c r="H316" s="18">
         <v>2001062</v>
       </c>
     </row>
     <row r="317" spans="1:8">
       <c r="A317" s="11" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="B317" s="11" t="s">
         <v>102</v>
@@ -10913,16 +10961,16 @@
       <c r="F317" s="11" t="s">
         <v>389</v>
       </c>
-      <c r="G317" s="19" t="s">
-        <v>677</v>
-      </c>
-      <c r="H317" s="17">
+      <c r="G317" s="20" t="s">
+        <v>675</v>
+      </c>
+      <c r="H317" s="18">
         <v>2001063</v>
       </c>
     </row>
     <row r="318" spans="1:8">
       <c r="A318" s="11" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="B318" s="11" t="s">
         <v>276</v>
@@ -10942,13 +10990,13 @@
       <c r="G318" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="H318" s="17">
+      <c r="H318" s="18">
         <v>2001064</v>
       </c>
     </row>
     <row r="319" spans="1:8">
       <c r="A319" s="11" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="B319" s="11" t="s">
         <v>35</v>
@@ -10968,13 +11016,13 @@
       <c r="G319" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="H319" s="17">
+      <c r="H319" s="18">
         <v>1006093</v>
       </c>
     </row>
     <row r="320" spans="1:8">
       <c r="A320" s="11" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="B320" s="11" t="s">
         <v>10</v>
@@ -10989,18 +11037,18 @@
         <v>8</v>
       </c>
       <c r="F320" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G320" s="9" t="s">
-        <v>611</v>
-      </c>
-      <c r="H320" s="17">
+        <v>612</v>
+      </c>
+      <c r="H320" s="18">
         <v>1001200</v>
       </c>
     </row>
     <row r="321" spans="1:8">
       <c r="A321" s="11" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B321" s="11" t="s">
         <v>10</v>
@@ -11015,18 +11063,18 @@
         <v>18</v>
       </c>
       <c r="F321" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G321" s="9" t="s">
-        <v>611</v>
-      </c>
-      <c r="H321" s="17">
+        <v>612</v>
+      </c>
+      <c r="H321" s="18">
         <v>1001201</v>
       </c>
     </row>
     <row r="322" spans="1:8">
       <c r="A322" s="11" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="B322" s="11" t="s">
         <v>10</v>
@@ -11041,18 +11089,18 @@
         <v>18</v>
       </c>
       <c r="F322" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G322" s="9" t="s">
-        <v>611</v>
-      </c>
-      <c r="H322" s="17">
+        <v>612</v>
+      </c>
+      <c r="H322" s="18">
         <v>1001202</v>
       </c>
     </row>
     <row r="323" spans="1:8">
       <c r="A323" s="11" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B323" s="11" t="s">
         <v>10</v>
@@ -11067,18 +11115,18 @@
         <v>3</v>
       </c>
       <c r="F323" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G323" s="9" t="s">
-        <v>611</v>
-      </c>
-      <c r="H323" s="17">
+        <v>612</v>
+      </c>
+      <c r="H323" s="18">
         <v>1001203</v>
       </c>
     </row>
     <row r="324" spans="1:8">
       <c r="A324" s="11" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="B324" s="11" t="s">
         <v>10</v>
@@ -11093,18 +11141,18 @@
         <v>8</v>
       </c>
       <c r="F324" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G324" s="9" t="s">
-        <v>611</v>
-      </c>
-      <c r="H324" s="17">
+        <v>612</v>
+      </c>
+      <c r="H324" s="18">
         <v>1001204</v>
       </c>
     </row>
     <row r="325" spans="1:8">
       <c r="A325" s="11" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="B325" s="11" t="s">
         <v>10</v>
@@ -11119,18 +11167,18 @@
         <v>8</v>
       </c>
       <c r="F325" s="11" t="s">
-        <v>613</v>
+        <v>127</v>
       </c>
       <c r="G325" s="9" t="s">
-        <v>611</v>
-      </c>
-      <c r="H325" s="17">
+        <v>612</v>
+      </c>
+      <c r="H325" s="18">
         <v>1001205</v>
       </c>
     </row>
     <row r="326" spans="1:8">
       <c r="A326" s="11" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="B326" s="11" t="s">
         <v>10</v>
@@ -11145,18 +11193,18 @@
         <v>3</v>
       </c>
       <c r="F326" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="G326" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="H326" s="17">
+        <v>127</v>
+      </c>
+      <c r="G326" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="H326" s="18">
         <v>1001206</v>
       </c>
     </row>
     <row r="327" spans="1:8">
       <c r="A327" s="11" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="B327" s="11" t="s">
         <v>10</v>
@@ -11171,18 +11219,18 @@
         <v>3</v>
       </c>
       <c r="F327" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="G327" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="H327" s="17">
+        <v>127</v>
+      </c>
+      <c r="G327" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="H327" s="18">
         <v>1001207</v>
       </c>
     </row>
     <row r="328" spans="1:8">
       <c r="A328" s="11" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="B328" s="11" t="s">
         <v>10</v>
@@ -11197,18 +11245,18 @@
         <v>18</v>
       </c>
       <c r="F328" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="G328" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="H328" s="17">
+        <v>127</v>
+      </c>
+      <c r="G328" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="H328" s="18">
         <v>1001208</v>
       </c>
     </row>
     <row r="329" spans="1:8">
       <c r="A329" s="11" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B329" s="11" t="s">
         <v>10</v>
@@ -11223,18 +11271,18 @@
         <v>5</v>
       </c>
       <c r="F329" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="G329" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="H329" s="17">
+        <v>127</v>
+      </c>
+      <c r="G329" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="H329" s="18">
         <v>1001209</v>
       </c>
     </row>
     <row r="330" spans="1:8">
       <c r="A330" s="11" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="B330" s="11" t="s">
         <v>10</v>
@@ -11249,18 +11297,18 @@
         <v>5</v>
       </c>
       <c r="F330" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="G330" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="H330" s="17">
+        <v>127</v>
+      </c>
+      <c r="G330" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="H330" s="18">
         <v>1001210</v>
       </c>
     </row>
     <row r="331" spans="1:8">
       <c r="A331" s="11" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="B331" s="11" t="s">
         <v>10</v>
@@ -11275,18 +11323,18 @@
         <v>5</v>
       </c>
       <c r="F331" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="G331" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="H331" s="17">
+        <v>127</v>
+      </c>
+      <c r="G331" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="H331" s="18">
         <v>1001211</v>
       </c>
     </row>
     <row r="332" spans="1:8">
       <c r="A332" s="11" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="B332" s="11" t="s">
         <v>10</v>
@@ -11301,18 +11349,18 @@
         <v>8</v>
       </c>
       <c r="F332" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="G332" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="H332" s="17">
+        <v>127</v>
+      </c>
+      <c r="G332" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="H332" s="18">
         <v>1001212</v>
       </c>
     </row>
     <row r="333" spans="1:8">
       <c r="A333" s="11" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B333" s="11" t="s">
         <v>10</v>
@@ -11327,12 +11375,12 @@
         <v>2</v>
       </c>
       <c r="F333" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="G333" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="H333" s="17">
+        <v>127</v>
+      </c>
+      <c r="G333" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="H333" s="18">
         <v>1001213</v>
       </c>
     </row>
@@ -11353,18 +11401,18 @@
         <v>8</v>
       </c>
       <c r="F334" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="G334" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="H334" s="17">
+        <v>127</v>
+      </c>
+      <c r="G334" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="H334" s="18">
         <v>1001214</v>
       </c>
     </row>
     <row r="335" spans="1:8">
       <c r="A335" s="11" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B335" s="11" t="s">
         <v>10</v>
@@ -11379,18 +11427,18 @@
         <v>6</v>
       </c>
       <c r="F335" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="G335" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="H335" s="17">
+        <v>127</v>
+      </c>
+      <c r="G335" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="H335" s="18">
         <v>1001215</v>
       </c>
     </row>
     <row r="336" spans="1:8">
       <c r="A336" s="11" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="B336" s="11" t="s">
         <v>10</v>
@@ -11405,12 +11453,12 @@
         <v>6</v>
       </c>
       <c r="F336" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="G336" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="H336" s="17">
+        <v>127</v>
+      </c>
+      <c r="G336" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="H336" s="18">
         <v>1001216</v>
       </c>
     </row>
@@ -11431,18 +11479,18 @@
         <v>6</v>
       </c>
       <c r="F337" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="G337" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="H337" s="17">
+        <v>127</v>
+      </c>
+      <c r="G337" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="H337" s="18">
         <v>1001217</v>
       </c>
     </row>
     <row r="338" spans="1:8">
       <c r="A338" s="11" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="B338" s="11" t="s">
         <v>10</v>
@@ -11457,12 +11505,12 @@
         <v>4</v>
       </c>
       <c r="F338" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="G338" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="H338" s="17">
+        <v>127</v>
+      </c>
+      <c r="G338" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="H338" s="18">
         <v>1001218</v>
       </c>
     </row>
@@ -11483,18 +11531,18 @@
         <v>3</v>
       </c>
       <c r="F339" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="G339" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="H339" s="17">
+        <v>127</v>
+      </c>
+      <c r="G339" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="H339" s="18">
         <v>1001219</v>
       </c>
     </row>
     <row r="340" spans="1:8">
       <c r="A340" s="11" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="B340" s="11" t="s">
         <v>10</v>
@@ -11509,18 +11557,18 @@
         <v>3</v>
       </c>
       <c r="F340" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="G340" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="H340" s="17">
+        <v>127</v>
+      </c>
+      <c r="G340" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="H340" s="18">
         <v>1001220</v>
       </c>
     </row>
     <row r="341" spans="1:8">
       <c r="A341" s="11" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B341" s="11" t="s">
         <v>35</v>
@@ -11535,18 +11583,18 @@
         <v>18</v>
       </c>
       <c r="F341" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="G341" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="H341" s="17">
+        <v>127</v>
+      </c>
+      <c r="G341" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="H341" s="18">
         <v>1001221</v>
       </c>
     </row>
     <row r="342" spans="1:8">
       <c r="A342" s="11" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="B342" s="11" t="s">
         <v>10</v>
@@ -11561,18 +11609,18 @@
         <v>5</v>
       </c>
       <c r="F342" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="G342" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="H342" s="17">
+        <v>127</v>
+      </c>
+      <c r="G342" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="H342" s="18">
         <v>1001222</v>
       </c>
     </row>
     <row r="343" spans="1:8">
       <c r="A343" s="11" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B343" s="11" t="s">
         <v>10</v>
@@ -11587,18 +11635,18 @@
         <v>5</v>
       </c>
       <c r="F343" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="G343" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="H343" s="17">
+        <v>127</v>
+      </c>
+      <c r="G343" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="H343" s="18">
         <v>1001223</v>
       </c>
     </row>
     <row r="344" spans="1:8">
       <c r="A344" s="11" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="B344" s="11" t="s">
         <v>10</v>
@@ -11613,18 +11661,18 @@
         <v>18</v>
       </c>
       <c r="F344" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="G344" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="H344" s="17">
+        <v>127</v>
+      </c>
+      <c r="G344" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="H344" s="18">
         <v>1001224</v>
       </c>
     </row>
     <row r="345" spans="1:8">
       <c r="A345" s="11" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B345" s="11" t="s">
         <v>112</v>
@@ -11644,13 +11692,13 @@
       <c r="G345" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="H345" s="17">
+      <c r="H345" s="18">
         <v>1009032</v>
       </c>
     </row>
     <row r="346" spans="1:8">
       <c r="A346" s="11" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="B346" s="11" t="s">
         <v>35</v>
@@ -11670,13 +11718,13 @@
       <c r="G346" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="H346" s="17">
+      <c r="H346" s="18">
         <v>1009033</v>
       </c>
     </row>
     <row r="347" spans="1:8">
       <c r="A347" s="11" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="B347" s="11" t="s">
         <v>35</v>
@@ -11693,16 +11741,16 @@
       <c r="F347" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G347" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="H347" s="17">
+      <c r="G347" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="H347" s="18">
         <v>1009040</v>
       </c>
     </row>
     <row r="348" spans="1:8">
       <c r="A348" s="11" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="B348" s="11" t="s">
         <v>10</v>
@@ -11717,18 +11765,18 @@
         <v>10</v>
       </c>
       <c r="F348" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="G348" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="H348" s="17">
+        <v>127</v>
+      </c>
+      <c r="G348" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="H348" s="18">
         <v>1003029</v>
       </c>
     </row>
     <row r="349" spans="1:8">
       <c r="A349" s="11" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="B349" s="11" t="s">
         <v>10</v>
@@ -11743,118 +11791,384 @@
         <v>54</v>
       </c>
       <c r="F349" s="11" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="G349" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="H349" s="17">
+      <c r="H349" s="18">
         <v>1003028</v>
       </c>
     </row>
     <row r="350" spans="1:8">
-      <c r="A350" s="11" t="s"/>
-      <c r="B350" s="11" t="s"/>
-      <c r="C350" s="9" t="s"/>
-      <c r="D350" s="11" t="s"/>
-      <c r="E350" s="11" t="s"/>
-      <c r="F350" s="11" t="s"/>
-      <c r="G350" s="9" t="s"/>
-      <c r="H350" s="17" t="s"/>
+      <c r="A350" s="11" t="s">
+        <v>719</v>
+      </c>
+      <c r="B350" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C350" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="D350" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E350" s="11">
+        <v>14.8</v>
+      </c>
+      <c r="F350" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="G350" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="H350" s="18">
+        <v>1004004</v>
+      </c>
     </row>
     <row r="351" spans="1:8">
-      <c r="A351" s="11" t="s"/>
-      <c r="B351" s="11" t="s"/>
-      <c r="C351" s="9" t="s"/>
-      <c r="D351" s="11" t="s"/>
-      <c r="E351" s="11" t="s"/>
-      <c r="F351" s="11" t="s"/>
-      <c r="G351" s="9" t="s"/>
-      <c r="H351" s="17" t="s"/>
+      <c r="A351" s="11" t="s">
+        <v>720</v>
+      </c>
+      <c r="B351" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C351" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D351" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E351" s="11">
+        <v>3</v>
+      </c>
+      <c r="F351" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="G351" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="H351" s="18">
+        <v>1001225</v>
+      </c>
     </row>
     <row r="352" spans="1:8">
-      <c r="A352" s="11" t="s"/>
-      <c r="B352" s="11" t="s"/>
-      <c r="C352" s="9" t="s"/>
-      <c r="D352" s="11" t="s"/>
-      <c r="E352" s="11" t="s"/>
-      <c r="F352" s="11" t="s"/>
-      <c r="G352" s="9" t="s"/>
-      <c r="H352" s="17" t="s"/>
+      <c r="A352" s="11" t="s">
+        <v>721</v>
+      </c>
+      <c r="B352" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C352" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D352" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E352" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="F352" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="G352" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="H352" s="18">
+        <v>1001226</v>
+      </c>
     </row>
     <row r="353" spans="1:8">
-      <c r="A353" s="11" t="s"/>
-      <c r="B353" s="11" t="s"/>
-      <c r="C353" s="9" t="s"/>
-      <c r="D353" s="11" t="s"/>
-      <c r="E353" s="11" t="s"/>
-      <c r="F353" s="11" t="s"/>
-      <c r="G353" s="9" t="s"/>
-      <c r="H353" s="17" t="s"/>
+      <c r="A353" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="B353" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C353" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D353" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E353" s="11">
+        <v>4</v>
+      </c>
+      <c r="F353" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="G353" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="H353" s="18">
+        <v>1001227</v>
+      </c>
     </row>
     <row r="354" spans="1:8">
-      <c r="A354" s="11" t="s"/>
-      <c r="B354" s="11" t="s"/>
-      <c r="C354" s="9" t="s"/>
-      <c r="D354" s="11" t="s"/>
-      <c r="E354" s="11" t="s"/>
-      <c r="F354" s="11" t="s"/>
-      <c r="G354" s="9" t="s"/>
-      <c r="H354" s="17" t="s"/>
+      <c r="A354" s="11" t="s">
+        <v>723</v>
+      </c>
+      <c r="B354" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C354" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D354" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E354" s="11">
+        <v>17</v>
+      </c>
+      <c r="F354" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="G354" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="H354" s="18">
+        <v>1003030</v>
+      </c>
     </row>
     <row r="355" spans="1:8">
-      <c r="A355" s="11" t="s"/>
-      <c r="B355" s="11" t="s"/>
-      <c r="C355" s="9" t="s"/>
-      <c r="D355" s="11" t="s"/>
-      <c r="E355" s="11" t="s"/>
-      <c r="F355" s="11" t="s"/>
-      <c r="G355" s="9" t="s"/>
-      <c r="H355" s="17" t="s"/>
+      <c r="A355" s="11" t="s">
+        <v>724</v>
+      </c>
+      <c r="B355" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C355" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D355" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E355" s="11">
+        <v>3.3</v>
+      </c>
+      <c r="F355" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="G355" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="H355" s="18">
+        <v>1001228</v>
+      </c>
     </row>
     <row r="356" spans="1:8">
-      <c r="A356" s="11" t="s"/>
-      <c r="B356" s="11" t="s"/>
-      <c r="C356" s="9" t="s"/>
-      <c r="D356" s="11" t="s"/>
-      <c r="E356" s="11" t="s"/>
-      <c r="F356" s="11" t="s"/>
-      <c r="G356" s="9" t="s"/>
-      <c r="H356" s="17" t="s"/>
+      <c r="A356" s="11" t="s">
+        <v>725</v>
+      </c>
+      <c r="B356" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C356" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D356" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E356" s="11">
+        <v>31.5</v>
+      </c>
+      <c r="F356" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="G356" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="H356" s="18">
+        <v>1006094</v>
+      </c>
     </row>
     <row r="357" spans="1:8">
-      <c r="A357" s="11" t="s"/>
-      <c r="B357" s="11" t="s"/>
-      <c r="C357" s="9" t="s"/>
-      <c r="D357" s="11" t="s"/>
-      <c r="E357" s="11" t="s"/>
-      <c r="F357" s="11" t="s"/>
-      <c r="G357" s="9" t="s"/>
-      <c r="H357" s="17" t="s"/>
+      <c r="A357" s="11" t="s">
+        <v>726</v>
+      </c>
+      <c r="B357" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C357" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D357" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E357" s="11">
+        <v>15</v>
+      </c>
+      <c r="F357" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="G357" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="H357" s="18">
+        <v>1001229</v>
+      </c>
     </row>
     <row r="358" spans="1:8">
-      <c r="A358" s="11" t="s"/>
-      <c r="B358" s="11" t="s"/>
-      <c r="C358" s="9" t="s"/>
-      <c r="D358" s="11" t="s"/>
-      <c r="E358" s="11" t="s"/>
-      <c r="F358" s="11" t="s"/>
-      <c r="G358" s="9" t="s"/>
-      <c r="H358" s="17" t="s"/>
+      <c r="A358" s="11" t="s">
+        <v>727</v>
+      </c>
+      <c r="B358" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C358" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D358" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E358" s="11">
+        <v>22</v>
+      </c>
+      <c r="F358" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="G358" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="H358" s="18">
+        <v>1006095</v>
+      </c>
     </row>
     <row r="359" spans="1:8">
-      <c r="A359" s="11" t="s"/>
-      <c r="B359" s="11" t="s"/>
-      <c r="C359" s="9" t="s"/>
-      <c r="D359" s="11" t="s"/>
-      <c r="E359" s="11" t="s"/>
-      <c r="F359" s="11" t="s"/>
-      <c r="G359" s="9" t="s"/>
-      <c r="H359" s="17" t="s"/>
+      <c r="A359" s="11" t="s">
+        <v>728</v>
+      </c>
+      <c r="B359" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="C359" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D359" s="11" t="s">
+        <v>729</v>
+      </c>
+      <c r="E359" s="11">
+        <v>320</v>
+      </c>
+      <c r="F359" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="G359" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="H359" s="18">
+        <v>1009041</v>
+      </c>
+    </row>
+    <row r="360" spans="1:8">
+      <c r="A360" s="11" t="s">
+        <v>730</v>
+      </c>
+      <c r="B360" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="C360" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D360" s="11" t="s">
+        <v>731</v>
+      </c>
+      <c r="E360" s="11">
+        <v>430</v>
+      </c>
+      <c r="F360" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="G360" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="H360" s="18">
+        <v>1009042</v>
+      </c>
+    </row>
+    <row r="361" spans="1:8">
+      <c r="A361" s="11" t="s"/>
+      <c r="B361" s="11" t="s"/>
+      <c r="C361" s="9" t="s"/>
+      <c r="D361" s="11" t="s"/>
+      <c r="E361" s="11" t="s"/>
+      <c r="F361" s="11" t="s"/>
+      <c r="G361" s="9" t="s"/>
+      <c r="H361" s="18" t="s"/>
+    </row>
+    <row r="362" spans="1:8">
+      <c r="A362" s="11" t="s"/>
+      <c r="B362" s="11" t="s"/>
+      <c r="C362" s="9" t="s"/>
+      <c r="D362" s="11" t="s"/>
+      <c r="E362" s="11" t="s"/>
+      <c r="F362" s="11" t="s"/>
+      <c r="G362" s="9" t="s"/>
+      <c r="H362" s="18" t="s"/>
+    </row>
+    <row r="363" spans="1:8">
+      <c r="A363" s="11" t="s"/>
+      <c r="B363" s="11" t="s"/>
+      <c r="C363" s="9" t="s"/>
+      <c r="D363" s="11" t="s"/>
+      <c r="E363" s="11" t="s"/>
+      <c r="F363" s="11" t="s"/>
+      <c r="G363" s="9" t="s"/>
+      <c r="H363" s="18" t="s"/>
+    </row>
+    <row r="364" spans="1:8">
+      <c r="A364" s="11" t="s"/>
+      <c r="B364" s="11" t="s"/>
+      <c r="C364" s="9" t="s"/>
+      <c r="D364" s="11" t="s"/>
+      <c r="E364" s="11" t="s"/>
+      <c r="F364" s="11" t="s"/>
+      <c r="G364" s="9" t="s"/>
+      <c r="H364" s="18" t="s"/>
+    </row>
+    <row r="365" spans="1:8">
+      <c r="A365" s="11" t="s"/>
+      <c r="B365" s="11" t="s"/>
+      <c r="C365" s="9" t="s"/>
+      <c r="D365" s="11" t="s"/>
+      <c r="E365" s="11" t="s"/>
+      <c r="F365" s="11" t="s"/>
+      <c r="G365" s="9" t="s"/>
+      <c r="H365" s="18" t="s"/>
+    </row>
+    <row r="366" spans="1:8">
+      <c r="A366" s="11" t="s"/>
+      <c r="B366" s="11" t="s"/>
+      <c r="C366" s="9" t="s"/>
+      <c r="D366" s="11" t="s"/>
+      <c r="E366" s="11" t="s"/>
+      <c r="F366" s="11" t="s"/>
+      <c r="G366" s="9" t="s"/>
+      <c r="H366" s="18" t="s"/>
+    </row>
+    <row r="367" spans="1:8">
+      <c r="A367" s="11" t="s"/>
+      <c r="B367" s="11" t="s"/>
+      <c r="C367" s="9" t="s"/>
+      <c r="D367" s="11" t="s"/>
+      <c r="E367" s="11" t="s"/>
+      <c r="F367" s="11" t="s"/>
+      <c r="G367" s="9" t="s"/>
+      <c r="H367" s="18" t="s"/>
+    </row>
+    <row r="368" spans="1:8">
+      <c r="A368" s="11" t="s"/>
+      <c r="B368" s="11" t="s"/>
+      <c r="C368" s="9" t="s"/>
+      <c r="D368" s="11" t="s"/>
+      <c r="E368" s="11" t="s"/>
+      <c r="F368" s="11" t="s"/>
+      <c r="G368" s="9" t="s"/>
+      <c r="H368" s="18" t="s"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H349">
-    <sortState ref="A2:H349"/>
+  <autoFilter ref="A1:H360">
+    <sortState ref="A2:H360"/>
   </autoFilter>
   <ignoredErrors>
     <ignoredError sqref="B1" numberStoredAsText="1"/>
@@ -12613,7 +12927,6 @@
     <ignoredError sqref="F99" numberStoredAsText="1"/>
     <ignoredError sqref="G99" numberStoredAsText="1"/>
     <ignoredError sqref="H99" numberStoredAsText="1"/>
-    <ignoredError sqref="A100" numberStoredAsText="1"/>
     <ignoredError sqref="B100" numberStoredAsText="1"/>
     <ignoredError sqref="C100" numberStoredAsText="1"/>
     <ignoredError sqref="F100" numberStoredAsText="1"/>
@@ -12731,10 +13044,8 @@
     <ignoredError sqref="F115" numberStoredAsText="1"/>
     <ignoredError sqref="G115" numberStoredAsText="1"/>
     <ignoredError sqref="H115" numberStoredAsText="1"/>
-    <ignoredError sqref="A116" numberStoredAsText="1"/>
     <ignoredError sqref="B116" numberStoredAsText="1"/>
     <ignoredError sqref="C116" numberStoredAsText="1"/>
-    <ignoredError sqref="D116" numberStoredAsText="1"/>
     <ignoredError sqref="E116" numberStoredAsText="1"/>
     <ignoredError sqref="F116" numberStoredAsText="1"/>
     <ignoredError sqref="G116" numberStoredAsText="1"/>
@@ -12822,10 +13133,8 @@
     <ignoredError sqref="F128" numberStoredAsText="1"/>
     <ignoredError sqref="G128" numberStoredAsText="1"/>
     <ignoredError sqref="H128" numberStoredAsText="1"/>
-    <ignoredError sqref="A129" numberStoredAsText="1"/>
     <ignoredError sqref="B129" numberStoredAsText="1"/>
     <ignoredError sqref="C129" numberStoredAsText="1"/>
-    <ignoredError sqref="D129" numberStoredAsText="1"/>
     <ignoredError sqref="E129" numberStoredAsText="1"/>
     <ignoredError sqref="F129" numberStoredAsText="1"/>
     <ignoredError sqref="G129" numberStoredAsText="1"/>
@@ -13722,7 +14031,6 @@
     <ignoredError sqref="A251" numberStoredAsText="1"/>
     <ignoredError sqref="B251" numberStoredAsText="1"/>
     <ignoredError sqref="D251" numberStoredAsText="1"/>
-    <ignoredError sqref="E251" numberStoredAsText="1"/>
     <ignoredError sqref="F251" numberStoredAsText="1"/>
     <ignoredError sqref="G251" numberStoredAsText="1"/>
     <ignoredError sqref="H251" numberStoredAsText="1"/>
@@ -13808,80 +14116,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.75" customHeight="1">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="E1" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="22" t="s">
+      <c r="G1" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="H1" s="23" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="23">
+      <c r="B2" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="24">
         <v>17.5</v>
       </c>
-      <c r="F2" s="22" t="s">
+      <c r="F2" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="22" t="s">
+      <c r="G2" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="22" t="s">
+      <c r="H2" s="23" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="24" t="s">
-        <v>721</v>
-      </c>
-      <c r="B3" s="22" t="s">
+      <c r="A3" s="25" t="s">
+        <v>732</v>
+      </c>
+      <c r="B3" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="23">
+      <c r="E3" s="24">
         <v>115</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="22" t="s">
+      <c r="G3" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="22" t="s">
+      <c r="H3" s="23" t="s">
         <v>22</v>
       </c>
     </row>
